--- a/Exp3_PTO_GRPO/eda/results/arms/training/tables/gpt-4o-mini/training.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/training/tables/gpt-4o-mini/training.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1017,37 +1017,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>7574</v>
+        <v>9376</v>
       </c>
       <c r="E17" t="n">
-        <v>3.290739216204042</v>
+        <v>3.869958969082514</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8046651305316942</v>
+        <v>0.7937641384928806</v>
       </c>
       <c r="G17" t="n">
-        <v>2.352941176470588</v>
+        <v>2.588235294117647</v>
       </c>
       <c r="H17" t="n">
-        <v>3.311764705882353</v>
+        <v>4.176470588235293</v>
       </c>
       <c r="I17" t="n">
-        <v>4.435294117647059</v>
+        <v>4.794117647058823</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.01066552901023891</v>
       </c>
     </row>
     <row r="18">
@@ -1062,25 +1062,25 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>6168</v>
+        <v>7574</v>
       </c>
       <c r="E18" t="n">
-        <v>3.33243209735256</v>
+        <v>3.290739216204042</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7666601470607851</v>
+        <v>0.8046651305316942</v>
       </c>
       <c r="G18" t="n">
-        <v>2.302352941176471</v>
+        <v>2.352941176470588</v>
       </c>
       <c r="H18" t="n">
-        <v>3.435294117647059</v>
+        <v>3.311764705882353</v>
       </c>
       <c r="I18" t="n">
-        <v>4.405882352941177</v>
+        <v>4.435294117647059</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1098,25 +1098,25 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>6277</v>
+        <v>6168</v>
       </c>
       <c r="E19" t="n">
-        <v>3.536591102906034</v>
+        <v>3.33243209735256</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6748374152512981</v>
+        <v>0.7666601470607851</v>
       </c>
       <c r="G19" t="n">
-        <v>2.647058823529412</v>
+        <v>2.302352941176471</v>
       </c>
       <c r="H19" t="n">
-        <v>3.470588235294118</v>
+        <v>3.435294117647059</v>
       </c>
       <c r="I19" t="n">
-        <v>4.476470588235294</v>
+        <v>4.405882352941177</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1134,25 +1134,25 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>5168</v>
+        <v>6277</v>
       </c>
       <c r="E20" t="n">
-        <v>3.663854489164087</v>
+        <v>3.536591102906034</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5430193468825506</v>
+        <v>0.6748374152512981</v>
       </c>
       <c r="G20" t="n">
-        <v>2.91764705882353</v>
+        <v>2.647058823529412</v>
       </c>
       <c r="H20" t="n">
-        <v>3.670588235294118</v>
+        <v>3.470588235294118</v>
       </c>
       <c r="I20" t="n">
-        <v>4.405882352941177</v>
+        <v>4.476470588235294</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1170,25 +1170,25 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>4792</v>
+        <v>5168</v>
       </c>
       <c r="E21" t="n">
-        <v>3.743944564470195</v>
+        <v>3.663854489164087</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5762331485203405</v>
+        <v>0.5430193468825506</v>
       </c>
       <c r="G21" t="n">
-        <v>2.976470588235294</v>
+        <v>2.91764705882353</v>
       </c>
       <c r="H21" t="n">
-        <v>3.7</v>
+        <v>3.670588235294118</v>
       </c>
       <c r="I21" t="n">
-        <v>4.564705882352941</v>
+        <v>4.405882352941177</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1206,25 +1206,25 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>4718</v>
+        <v>4792</v>
       </c>
       <c r="E22" t="n">
-        <v>3.776677555295115</v>
+        <v>3.743944564470195</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5295341015127092</v>
+        <v>0.5762331485203405</v>
       </c>
       <c r="G22" t="n">
-        <v>3.076470588235294</v>
+        <v>2.976470588235294</v>
       </c>
       <c r="H22" t="n">
-        <v>3.735294117647059</v>
+        <v>3.7</v>
       </c>
       <c r="I22" t="n">
-        <v>4.552941176470588</v>
+        <v>4.564705882352941</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1242,25 +1242,25 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>4158</v>
+        <v>4718</v>
       </c>
       <c r="E23" t="n">
-        <v>3.889255298078827</v>
+        <v>3.776677555295115</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5741195003775807</v>
+        <v>0.5295341015127092</v>
       </c>
       <c r="G23" t="n">
-        <v>3.111764705882353</v>
+        <v>3.076470588235294</v>
       </c>
       <c r="H23" t="n">
-        <v>3.858823529411764</v>
+        <v>3.735294117647059</v>
       </c>
       <c r="I23" t="n">
-        <v>4.623529411764705</v>
+        <v>4.552941176470588</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>4114</v>
+        <v>4158</v>
       </c>
       <c r="E24" t="n">
-        <v>4.005326146015042</v>
+        <v>3.889255298078827</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5416210462718096</v>
+        <v>0.5741195003775807</v>
       </c>
       <c r="G24" t="n">
-        <v>3.370588235294118</v>
+        <v>3.111764705882353</v>
       </c>
       <c r="H24" t="n">
         <v>3.858823529411764</v>
       </c>
       <c r="I24" t="n">
-        <v>4.823529411764707</v>
+        <v>4.623529411764705</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1314,25 +1314,25 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>3556</v>
+        <v>4114</v>
       </c>
       <c r="E25" t="n">
-        <v>3.999240719910011</v>
+        <v>4.005326146015042</v>
       </c>
       <c r="F25" t="n">
-        <v>0.513138129373051</v>
+        <v>0.5416210462718096</v>
       </c>
       <c r="G25" t="n">
-        <v>3.391176470588235</v>
+        <v>3.370588235294118</v>
       </c>
       <c r="H25" t="n">
-        <v>3.947058823529412</v>
+        <v>3.858823529411764</v>
       </c>
       <c r="I25" t="n">
-        <v>4.852941176470589</v>
+        <v>4.823529411764707</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1350,22 +1350,22 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>3261</v>
+        <v>3556</v>
       </c>
       <c r="E26" t="n">
-        <v>4.077670148096037</v>
+        <v>3.999240719910011</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5552196216842494</v>
+        <v>0.513138129373051</v>
       </c>
       <c r="G26" t="n">
-        <v>3.329411764705882</v>
+        <v>3.391176470588235</v>
       </c>
       <c r="H26" t="n">
-        <v>4.117647058823529</v>
+        <v>3.947058823529412</v>
       </c>
       <c r="I26" t="n">
         <v>4.852941176470589</v>
@@ -1377,7 +1377,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1386,25 +1386,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>7097</v>
+        <v>3261</v>
       </c>
       <c r="E27" t="n">
-        <v>3.291063332476854</v>
+        <v>4.077670148096037</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9647864799567627</v>
+        <v>0.5552196216842494</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>3.329411764705882</v>
       </c>
       <c r="H27" t="n">
-        <v>3.435294117647059</v>
+        <v>4.117647058823529</v>
       </c>
       <c r="I27" t="n">
-        <v>4.535294117647059</v>
+        <v>4.852941176470589</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1422,25 +1422,25 @@
         </is>
       </c>
       <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7097</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.291063332476854</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.9647864799567627</v>
+      </c>
+      <c r="G28" t="n">
         <v>2</v>
       </c>
-      <c r="D28" t="n">
-        <v>6685</v>
-      </c>
-      <c r="E28" t="n">
-        <v>3.473938140701307</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.8816031388249556</v>
-      </c>
-      <c r="G28" t="n">
-        <v>2.310588235294118</v>
-      </c>
       <c r="H28" t="n">
-        <v>3.505882352941176</v>
+        <v>3.435294117647059</v>
       </c>
       <c r="I28" t="n">
-        <v>4.564705882352941</v>
+        <v>4.535294117647059</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1458,25 +1458,25 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>6522</v>
+        <v>6685</v>
       </c>
       <c r="E29" t="n">
-        <v>3.559655103991918</v>
+        <v>3.473938140701307</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8483398044383608</v>
+        <v>0.8816031388249556</v>
       </c>
       <c r="G29" t="n">
-        <v>2.382352941176471</v>
+        <v>2.310588235294118</v>
       </c>
       <c r="H29" t="n">
-        <v>3.623529411764706</v>
+        <v>3.505882352941176</v>
       </c>
       <c r="I29" t="n">
-        <v>4.594117647058823</v>
+        <v>4.564705882352941</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1494,25 +1494,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>4899</v>
+        <v>6522</v>
       </c>
       <c r="E30" t="n">
-        <v>3.789291932327125</v>
+        <v>3.559655103991918</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7231635892705964</v>
+        <v>0.8483398044383608</v>
       </c>
       <c r="G30" t="n">
-        <v>2.758823529411765</v>
+        <v>2.382352941176471</v>
       </c>
       <c r="H30" t="n">
-        <v>3.841176470588235</v>
+        <v>3.623529411764706</v>
       </c>
       <c r="I30" t="n">
-        <v>4.652941176470588</v>
+        <v>4.594117647058823</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1530,25 +1530,25 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>3351</v>
+        <v>4899</v>
       </c>
       <c r="E31" t="n">
-        <v>3.866575385749644</v>
+        <v>3.789291932327125</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7382916147127863</v>
+        <v>0.7231635892705964</v>
       </c>
       <c r="G31" t="n">
-        <v>2.817647058823529</v>
+        <v>2.758823529411765</v>
       </c>
       <c r="H31" t="n">
-        <v>3.982352941176471</v>
+        <v>3.841176470588235</v>
       </c>
       <c r="I31" t="n">
-        <v>4.794117647058823</v>
+        <v>4.652941176470588</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>5289</v>
+        <v>3351</v>
       </c>
       <c r="E32" t="n">
-        <v>3.927499916586033</v>
+        <v>3.866575385749644</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7053329596308401</v>
+        <v>0.7382916147127863</v>
       </c>
       <c r="G32" t="n">
         <v>2.817647058823529</v>
       </c>
       <c r="H32" t="n">
-        <v>4.076470588235294</v>
+        <v>3.982352941176471</v>
       </c>
       <c r="I32" t="n">
         <v>4.794117647058823</v>
@@ -1602,25 +1602,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>6444</v>
+        <v>5289</v>
       </c>
       <c r="E33" t="n">
-        <v>3.996886296418009</v>
+        <v>3.927499916586033</v>
       </c>
       <c r="F33" t="n">
-        <v>0.699194486280059</v>
+        <v>0.7053329596308401</v>
       </c>
       <c r="G33" t="n">
-        <v>2.847058823529411</v>
+        <v>2.817647058823529</v>
       </c>
       <c r="H33" t="n">
-        <v>4.158823529411764</v>
+        <v>4.076470588235294</v>
       </c>
       <c r="I33" t="n">
-        <v>4.882352941176471</v>
+        <v>4.794117647058823</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1638,25 +1638,25 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D34" t="n">
-        <v>6117</v>
+        <v>6444</v>
       </c>
       <c r="E34" t="n">
-        <v>4.173726067180183</v>
+        <v>3.996886296418009</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7248460576901864</v>
+        <v>0.699194486280059</v>
       </c>
       <c r="G34" t="n">
-        <v>2.817647058823529</v>
+        <v>2.847058823529411</v>
       </c>
       <c r="H34" t="n">
-        <v>4.376470588235295</v>
+        <v>4.158823529411764</v>
       </c>
       <c r="I34" t="n">
-        <v>4.911764705882353</v>
+        <v>4.882352941176471</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1674,25 +1674,25 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>6077</v>
+        <v>6117</v>
       </c>
       <c r="E35" t="n">
-        <v>4.104804034498446</v>
+        <v>4.173726067180183</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6493581191361258</v>
+        <v>0.7248460576901864</v>
       </c>
       <c r="G35" t="n">
-        <v>2.947058823529412</v>
+        <v>2.817647058823529</v>
       </c>
       <c r="H35" t="n">
-        <v>4.276470588235294</v>
+        <v>4.376470588235295</v>
       </c>
       <c r="I35" t="n">
-        <v>4.852941176470589</v>
+        <v>4.911764705882353</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1710,27 +1710,63 @@
         </is>
       </c>
       <c r="C36" t="n">
+        <v>9</v>
+      </c>
+      <c r="D36" t="n">
+        <v>6077</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4.104804034498446</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.6493581191361258</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.947058823529412</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4.276470588235294</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4.852941176470589</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
         <v>10</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D37" t="n">
         <v>7387</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E37" t="n">
         <v>4.320434945333217</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F37" t="n">
         <v>0.6017010582352287</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G37" t="n">
         <v>3.441176470588236</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H37" t="n">
         <v>4.464705882352941</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I37" t="n">
         <v>4.911764705882353</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1745,7 +1781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2158,28 +2194,25 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.1248888466358123</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2735077171015929</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.3217316082443207</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.2764705882352937</v>
-      </c>
-      <c r="I17" t="n">
-        <v>782</v>
+        <v>0.3710098373820518</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.01109215017064846</v>
       </c>
     </row>
     <row r="18">
@@ -2194,19 +2227,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2502057299603779</v>
+        <v>0.2735077171015929</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2988387588044927</v>
+        <v>0.3217316082443207</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2588235294117647</v>
+        <v>0.2764705882352937</v>
       </c>
       <c r="I18" t="n">
-        <v>618</v>
+        <v>782</v>
       </c>
     </row>
     <row r="19">
@@ -2221,19 +2254,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>0.24403916585694</v>
+        <v>0.2502057299603779</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2945635673624288</v>
+        <v>0.2988387588044927</v>
       </c>
       <c r="H19" t="n">
         <v>0.2588235294117647</v>
       </c>
       <c r="I19" t="n">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="20">
@@ -2248,19 +2281,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2317847077007</v>
+        <v>0.24403916585694</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2689969271290605</v>
+        <v>0.2945635673624288</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2352941176470589</v>
+        <v>0.2588235294117647</v>
       </c>
       <c r="I20" t="n">
-        <v>536</v>
+        <v>620</v>
       </c>
     </row>
     <row r="21">
@@ -2275,19 +2308,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2366862745098039</v>
+        <v>0.2317847077007</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2812324929971988</v>
+        <v>0.2689969271290605</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2470588235294118</v>
+        <v>0.2352941176470589</v>
       </c>
       <c r="I21" t="n">
-        <v>483</v>
+        <v>536</v>
       </c>
     </row>
     <row r="22">
@@ -2302,19 +2335,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2253110381208321</v>
+        <v>0.2366862745098039</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2672693498452013</v>
+        <v>0.2812324929971988</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2352941176470589</v>
+        <v>0.2470588235294118</v>
       </c>
       <c r="I22" t="n">
-        <v>475</v>
+        <v>483</v>
       </c>
     </row>
     <row r="23">
@@ -2329,19 +2362,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2201648413684092</v>
+        <v>0.2253110381208321</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2718382352941177</v>
+        <v>0.2672693498452013</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2470588235294118</v>
+        <v>0.2352941176470589</v>
       </c>
       <c r="I23" t="n">
-        <v>400</v>
+        <v>475</v>
       </c>
     </row>
     <row r="24">
@@ -2356,19 +2389,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>0.195312322220958</v>
+        <v>0.2201648413684092</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2490765171503958</v>
+        <v>0.2718382352941177</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2294117647058824</v>
+        <v>0.2470588235294118</v>
       </c>
       <c r="I24" t="n">
-        <v>379</v>
+        <v>400</v>
       </c>
     </row>
     <row r="25">
@@ -2383,19 +2416,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2253363228699552</v>
+        <v>0.195312322220958</v>
       </c>
       <c r="G25" t="n">
-        <v>0.265716147955027</v>
+        <v>0.2490765171503958</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2470588235294109</v>
+        <v>0.2294117647058824</v>
       </c>
       <c r="I25" t="n">
-        <v>361</v>
+        <v>379</v>
       </c>
     </row>
     <row r="26">
@@ -2410,25 +2443,25 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1957532281205165</v>
+        <v>0.2253363228699552</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2667364454678668</v>
+        <v>0.265716147955027</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2294117647058824</v>
+        <v>0.2470588235294109</v>
       </c>
       <c r="I26" t="n">
-        <v>281</v>
+        <v>361</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2437,19 +2470,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4241705221414408</v>
+        <v>0.1957532281205165</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4512302036199095</v>
+        <v>0.2667364454678668</v>
       </c>
       <c r="H27" t="n">
-        <v>0.391176470588235</v>
+        <v>0.2294117647058824</v>
       </c>
       <c r="I27" t="n">
-        <v>832</v>
+        <v>281</v>
       </c>
     </row>
     <row r="28">
@@ -2464,19 +2497,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>0.431745027760208</v>
+        <v>0.4241705221414408</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4614169060940571</v>
+        <v>0.4512302036199095</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4058823529411766</v>
+        <v>0.391176470588235</v>
       </c>
       <c r="I28" t="n">
-        <v>778</v>
+        <v>832</v>
       </c>
     </row>
     <row r="29">
@@ -2491,19 +2524,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4447303921568627</v>
+        <v>0.431745027760208</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4704503676470588</v>
+        <v>0.4614169060940571</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3970588235294117</v>
+        <v>0.4058823529411766</v>
       </c>
       <c r="I29" t="n">
-        <v>768</v>
+        <v>778</v>
       </c>
     </row>
     <row r="30">
@@ -2518,19 +2551,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>0.396497457057864</v>
+        <v>0.4447303921568627</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4260474349597744</v>
+        <v>0.4704503676470588</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3588235294117643</v>
+        <v>0.3970588235294117</v>
       </c>
       <c r="I30" t="n">
-        <v>563</v>
+        <v>768</v>
       </c>
     </row>
     <row r="31">
@@ -2545,19 +2578,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3809829059829061</v>
+        <v>0.396497457057864</v>
       </c>
       <c r="G31" t="n">
-        <v>0.408632897603486</v>
+        <v>0.4260474349597744</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3529411764705881</v>
+        <v>0.3588235294117643</v>
       </c>
       <c r="I31" t="n">
-        <v>432</v>
+        <v>563</v>
       </c>
     </row>
     <row r="32">
@@ -2572,19 +2605,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3324017389761335</v>
+        <v>0.3809829059829061</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3789560894780448</v>
+        <v>0.408632897603486</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3235294117647058</v>
+        <v>0.3529411764705881</v>
       </c>
       <c r="I32" t="n">
-        <v>568</v>
+        <v>432</v>
       </c>
     </row>
     <row r="33">
@@ -2599,19 +2632,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3317515853925214</v>
+        <v>0.3324017389761335</v>
       </c>
       <c r="G33" t="n">
-        <v>0.381601639204303</v>
+        <v>0.3789560894780448</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3352941176470585</v>
+        <v>0.3235294117647058</v>
       </c>
       <c r="I33" t="n">
-        <v>689</v>
+        <v>568</v>
       </c>
     </row>
     <row r="34">
@@ -2626,19 +2659,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2731497814249559</v>
+        <v>0.3317515853925214</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3538677771993754</v>
+        <v>0.381601639204303</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2588235294117656</v>
+        <v>0.3352941176470585</v>
       </c>
       <c r="I34" t="n">
-        <v>565</v>
+        <v>689</v>
       </c>
     </row>
     <row r="35">
@@ -2653,19 +2686,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3020483883435108</v>
+        <v>0.2731497814249559</v>
       </c>
       <c r="G35" t="n">
-        <v>0.3677736657576938</v>
+        <v>0.3538677771993754</v>
       </c>
       <c r="H35" t="n">
-        <v>0.276470588235294</v>
+        <v>0.2588235294117656</v>
       </c>
       <c r="I35" t="n">
-        <v>604</v>
+        <v>565</v>
       </c>
     </row>
     <row r="36">
@@ -2680,18 +2713,45 @@
         </is>
       </c>
       <c r="C36" t="n">
+        <v>9</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.3020483883435108</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.3677736657576938</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.276470588235294</v>
+      </c>
+      <c r="I36" t="n">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
         <v>10</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E37" t="n">
         <v>0.2335662558760005</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G37" t="n">
         <v>0.3282486414338833</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H37" t="n">
         <v>0.2352941176470589</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I37" t="n">
         <v>617</v>
       </c>
     </row>
@@ -2706,7 +2766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3174,29 +3234,29 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>7592</v>
+        <v>9376</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.24</v>
+        <v>0.01</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G17" t="n">
-        <v>3.290739216204042</v>
+        <v>3.869958969082514</v>
       </c>
       <c r="H17" t="n">
-        <v>286.2219441517387</v>
+        <v>817.3654010238907</v>
       </c>
     </row>
     <row r="18">
@@ -3206,25 +3266,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>6176</v>
+        <v>7592</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.13</v>
+        <v>0.24</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>3.33243209735256</v>
+        <v>3.290739216204042</v>
       </c>
       <c r="H18" t="n">
-        <v>324.7984132124352</v>
+        <v>286.2219441517387</v>
       </c>
     </row>
     <row r="19">
@@ -3234,25 +3294,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>6296</v>
+        <v>6176</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3</v>
+        <v>0.13</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>3.536591102906034</v>
+        <v>3.33243209735256</v>
       </c>
       <c r="H19" t="n">
-        <v>345.3122617534943</v>
+        <v>324.7984132124352</v>
       </c>
     </row>
     <row r="20">
@@ -3262,25 +3322,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>5176</v>
+        <v>6296</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>3.663854489164087</v>
+        <v>3.536591102906034</v>
       </c>
       <c r="H20" t="n">
-        <v>398.2600463678516</v>
+        <v>345.3122617534943</v>
       </c>
     </row>
     <row r="21">
@@ -3290,25 +3350,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>4800</v>
+        <v>5176</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>3.743944564470195</v>
+        <v>3.663854489164087</v>
       </c>
       <c r="H21" t="n">
-        <v>534.891875</v>
+        <v>398.2600463678516</v>
       </c>
     </row>
     <row r="22">
@@ -3318,25 +3378,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>4728</v>
+        <v>4800</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>3.776677555295115</v>
+        <v>3.743944564470195</v>
       </c>
       <c r="H22" t="n">
-        <v>609.8616751269036</v>
+        <v>534.891875</v>
       </c>
     </row>
     <row r="23">
@@ -3346,25 +3406,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>4168</v>
+        <v>4728</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>3.889255298078827</v>
+        <v>3.776677555295115</v>
       </c>
       <c r="H23" t="n">
-        <v>740.5856525911709</v>
+        <v>609.8616751269036</v>
       </c>
     </row>
     <row r="24">
@@ -3374,25 +3434,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>4136</v>
+        <v>4168</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.53</v>
+        <v>0.24</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>4.005326146015042</v>
+        <v>3.889255298078827</v>
       </c>
       <c r="H24" t="n">
-        <v>697.2487911025145</v>
+        <v>740.5856525911709</v>
       </c>
     </row>
     <row r="25">
@@ -3402,25 +3462,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C25" t="n">
-        <v>3568</v>
+        <v>4136</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.34</v>
+        <v>0.53</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>3.999240719910011</v>
+        <v>4.005326146015042</v>
       </c>
       <c r="H25" t="n">
-        <v>808.7051569506726</v>
+        <v>697.2487911025145</v>
       </c>
     </row>
     <row r="26">
@@ -3430,53 +3490,53 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C26" t="n">
-        <v>3280</v>
+        <v>3568</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.58</v>
+        <v>0.34</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>4.077670148096037</v>
+        <v>3.999240719910011</v>
       </c>
       <c r="H26" t="n">
-        <v>829.6390243902439</v>
+        <v>808.7051569506726</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C27" t="n">
-        <v>7120</v>
+        <v>3280</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.32</v>
+        <v>0.58</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>3.291063332476854</v>
+        <v>4.077670148096037</v>
       </c>
       <c r="H27" t="n">
-        <v>305.6846910112359</v>
+        <v>829.6390243902439</v>
       </c>
     </row>
     <row r="28">
@@ -3486,25 +3546,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>6696</v>
+        <v>7120</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>3.473938140701307</v>
+        <v>3.291063332476854</v>
       </c>
       <c r="H28" t="n">
-        <v>363.8626045400239</v>
+        <v>305.6846910112359</v>
       </c>
     </row>
     <row r="29">
@@ -3514,25 +3574,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>6528</v>
+        <v>6696</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>3.559655103991918</v>
+        <v>3.473938140701307</v>
       </c>
       <c r="H29" t="n">
-        <v>445.0816482843137</v>
+        <v>363.8626045400239</v>
       </c>
     </row>
     <row r="30">
@@ -3542,25 +3602,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>4904</v>
+        <v>6528</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>3.789291932327125</v>
+        <v>3.559655103991918</v>
       </c>
       <c r="H30" t="n">
-        <v>561.2230831973899</v>
+        <v>445.0816482843137</v>
       </c>
     </row>
     <row r="31">
@@ -3570,25 +3630,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>3744</v>
+        <v>4904</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>3.866575385749644</v>
+        <v>3.789291932327125</v>
       </c>
       <c r="H31" t="n">
-        <v>632.4281517094017</v>
+        <v>561.2230831973899</v>
       </c>
     </row>
     <row r="32">
@@ -3598,25 +3658,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>5304</v>
+        <v>3744</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.28</v>
+        <v>0.11</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>3.927499916586033</v>
+        <v>3.866575385749644</v>
       </c>
       <c r="H32" t="n">
-        <v>752.7567873303168</v>
+        <v>632.4281517094017</v>
       </c>
     </row>
     <row r="33">
@@ -3626,25 +3686,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>6456</v>
+        <v>5304</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>3.996886296418009</v>
+        <v>3.927499916586033</v>
       </c>
       <c r="H33" t="n">
-        <v>836.0020136307311</v>
+        <v>752.7567873303168</v>
       </c>
     </row>
     <row r="34">
@@ -3654,25 +3714,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C34" t="n">
-        <v>6136</v>
+        <v>6456</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0.31</v>
+        <v>0.19</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>4.173726067180183</v>
+        <v>3.996886296418009</v>
       </c>
       <c r="H34" t="n">
-        <v>936.5017926988266</v>
+        <v>836.0020136307311</v>
       </c>
     </row>
     <row r="35">
@@ -3682,25 +3742,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C35" t="n">
-        <v>6088</v>
+        <v>6136</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0.18</v>
+        <v>0.31</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>4.104804034498446</v>
+        <v>4.173726067180183</v>
       </c>
       <c r="H35" t="n">
-        <v>960.3909329829172</v>
+        <v>936.5017926988266</v>
       </c>
     </row>
     <row r="36">
@@ -3710,24 +3770,52 @@
         </is>
       </c>
       <c r="B36" t="n">
+        <v>9</v>
+      </c>
+      <c r="C36" t="n">
+        <v>6088</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4.104804034498446</v>
+      </c>
+      <c r="H36" t="n">
+        <v>960.3909329829172</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
         <v>10</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C37" t="n">
         <v>7408</v>
       </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
         <v>0.28</v>
       </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
         <v>4.320434945333217</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H37" t="n">
         <v>1003.434260259179</v>
       </c>
     </row>
@@ -3780,7 +3868,7 @@
         <v>0.8599</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8638</v>
+        <v>0.8743</v>
       </c>
       <c r="D2" t="n">
         <v>0.8647</v>
@@ -3797,7 +3885,7 @@
         <v>0.872</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8846000000000001</v>
+        <v>0.8922</v>
       </c>
       <c r="D3" t="n">
         <v>0.8633999999999999</v>
@@ -3814,7 +3902,7 @@
         <v>0.8781</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8915</v>
+        <v>0.8989</v>
       </c>
       <c r="D4" t="n">
         <v>0.8577</v>
@@ -3831,7 +3919,7 @@
         <v>0.8758</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8946</v>
+        <v>0.8994</v>
       </c>
       <c r="D5" t="n">
         <v>0.8413</v>
@@ -3848,7 +3936,7 @@
         <v>0.8738</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8922</v>
+        <v>0.896</v>
       </c>
       <c r="D6" t="n">
         <v>0.8247</v>
@@ -3865,7 +3953,7 @@
         <v>0.8768</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8905999999999999</v>
+        <v>0.8932</v>
       </c>
       <c r="D7" t="n">
         <v>0.8084</v>
@@ -3882,7 +3970,7 @@
         <v>0.8754</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8939</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="D8" t="n">
         <v>0.7887999999999999</v>
@@ -3899,7 +3987,7 @@
         <v>0.8739</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9003</v>
+        <v>0.9013</v>
       </c>
       <c r="D9" t="n">
         <v>0.7868000000000001</v>
@@ -3916,7 +4004,7 @@
         <v>0.8672</v>
       </c>
       <c r="C10" t="n">
-        <v>0.896</v>
+        <v>0.895</v>
       </c>
       <c r="D10" t="n">
         <v>0.7837</v>
@@ -3933,7 +4021,7 @@
         <v>0.8738</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8971</v>
+        <v>0.8982</v>
       </c>
       <c r="D11" t="n">
         <v>0.7637</v>
@@ -3950,7 +4038,7 @@
         <v>0.8663</v>
       </c>
       <c r="C12" t="n">
-        <v>0.898</v>
+        <v>0.8991</v>
       </c>
       <c r="D12" t="n">
         <v>0.7633</v>
@@ -3967,7 +4055,7 @@
         <v>0.8737</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8999</v>
+        <v>0.9005</v>
       </c>
       <c r="D13" t="n">
         <v>0.7597</v>
@@ -3984,7 +4072,7 @@
         <v>0.8759</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9056</v>
+        <v>0.9058</v>
       </c>
       <c r="D14" t="n">
         <v>0.7668</v>
@@ -4001,7 +4089,7 @@
         <v>0.8725000000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9129</v>
+        <v>0.9145</v>
       </c>
       <c r="D15" t="n">
         <v>0.7654</v>
@@ -4018,7 +4106,7 @@
         <v>0.8822</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9243</v>
+        <v>0.9258</v>
       </c>
       <c r="D16" t="n">
         <v>0.7581</v>
@@ -4035,7 +4123,7 @@
         <v>0.8842</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9241</v>
+        <v>0.9254</v>
       </c>
       <c r="D17" t="n">
         <v>0.7376</v>
@@ -4052,7 +4140,7 @@
         <v>0.8744</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.9194</v>
       </c>
       <c r="D18" t="n">
         <v>0.7478</v>
@@ -4069,7 +4157,7 @@
         <v>0.8815</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9207</v>
+        <v>0.9223</v>
       </c>
       <c r="D19" t="n">
         <v>0.7574</v>
@@ -4086,7 +4174,7 @@
         <v>0.8925999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9293</v>
+        <v>0.9304</v>
       </c>
       <c r="D20" t="n">
         <v>0.7561</v>
@@ -4103,7 +4191,7 @@
         <v>0.8968</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9354</v>
+        <v>0.9357</v>
       </c>
     </row>
   </sheetData>
@@ -4472,10 +4560,10 @@
         <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8637560777957861</v>
+        <v>0.8743062220923924</v>
       </c>
       <c r="D22" t="n">
-        <v>19744</v>
+        <v>23963</v>
       </c>
     </row>
     <row r="23">
@@ -4488,10 +4576,10 @@
         <v>14</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8846050148287948</v>
+        <v>0.8922375641706497</v>
       </c>
       <c r="D23" t="n">
-        <v>18545</v>
+        <v>22596</v>
       </c>
     </row>
     <row r="24">
@@ -4504,10 +4592,10 @@
         <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8915152584230023</v>
+        <v>0.8989062961868164</v>
       </c>
       <c r="D24" t="n">
-        <v>17007</v>
+        <v>20298</v>
       </c>
     </row>
     <row r="25">
@@ -4520,10 +4608,10 @@
         <v>18</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8946044171093095</v>
+        <v>0.8994314360824112</v>
       </c>
       <c r="D25" t="n">
-        <v>14308</v>
+        <v>16357</v>
       </c>
     </row>
     <row r="26">
@@ -4536,10 +4624,10 @@
         <v>20</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8921652665866621</v>
+        <v>0.8959875340864822</v>
       </c>
       <c r="D26" t="n">
-        <v>11666</v>
+        <v>12835</v>
       </c>
     </row>
     <row r="27">
@@ -4552,10 +4640,10 @@
         <v>22</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8906457319770014</v>
+        <v>0.8932208620512293</v>
       </c>
       <c r="D27" t="n">
-        <v>9044</v>
+        <v>9721</v>
       </c>
     </row>
     <row r="28">
@@ -4568,10 +4656,10 @@
         <v>24</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8939169139465876</v>
+        <v>0.8946927374301676</v>
       </c>
       <c r="D28" t="n">
-        <v>6740</v>
+        <v>7160</v>
       </c>
     </row>
     <row r="29">
@@ -4584,10 +4672,10 @@
         <v>26</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9003079291762894</v>
+        <v>0.9012704174228675</v>
       </c>
       <c r="D29" t="n">
-        <v>5196</v>
+        <v>5510</v>
       </c>
     </row>
     <row r="30">
@@ -4600,10 +4688,10 @@
         <v>28</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8959524353990396</v>
+        <v>0.894954327968682</v>
       </c>
       <c r="D30" t="n">
-        <v>4373</v>
+        <v>4598</v>
       </c>
     </row>
     <row r="31">
@@ -4616,10 +4704,10 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8971395550418954</v>
+        <v>0.8982202447163515</v>
       </c>
       <c r="D31" t="n">
-        <v>3461</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="32">
@@ -4632,10 +4720,10 @@
         <v>32</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8980301274623407</v>
+        <v>0.8990997749437359</v>
       </c>
       <c r="D32" t="n">
-        <v>2589</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="33">
@@ -4648,10 +4736,10 @@
         <v>34</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8998541565386485</v>
+        <v>0.9005210800568451</v>
       </c>
       <c r="D33" t="n">
-        <v>2057</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="34">
@@ -4664,10 +4752,10 @@
         <v>36</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9055982436882547</v>
+        <v>0.9057619816908993</v>
       </c>
       <c r="D34" t="n">
-        <v>1822</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="35">
@@ -4680,10 +4768,10 @@
         <v>38</v>
       </c>
       <c r="C35" t="n">
-        <v>0.9129232895646164</v>
+        <v>0.9145183175033921</v>
       </c>
       <c r="D35" t="n">
-        <v>1447</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="36">
@@ -4696,10 +4784,10 @@
         <v>40</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9242658423493045</v>
+        <v>0.9258137774413323</v>
       </c>
       <c r="D36" t="n">
-        <v>1294</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="37">
@@ -4712,10 +4800,10 @@
         <v>42</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9241261722080136</v>
+        <v>0.9253981559094719</v>
       </c>
       <c r="D37" t="n">
-        <v>1173</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="38">
@@ -4728,10 +4816,10 @@
         <v>44</v>
       </c>
       <c r="C38" t="n">
-        <v>0.9178470254957507</v>
+        <v>0.9193697868396663</v>
       </c>
       <c r="D38" t="n">
-        <v>1059</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="39">
@@ -4744,10 +4832,10 @@
         <v>46</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9207003089598352</v>
+        <v>0.9223007063572149</v>
       </c>
       <c r="D39" t="n">
-        <v>971</v>
+        <v>991</v>
       </c>
     </row>
     <row r="40">
@@ -4760,10 +4848,10 @@
         <v>48</v>
       </c>
       <c r="C40" t="n">
-        <v>0.929324894514768</v>
+        <v>0.9303534303534303</v>
       </c>
       <c r="D40" t="n">
-        <v>948</v>
+        <v>962</v>
       </c>
     </row>
     <row r="41">
@@ -4776,10 +4864,10 @@
         <v>50</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9353701527614571</v>
+        <v>0.935672514619883</v>
       </c>
       <c r="D41" t="n">
-        <v>851</v>
+        <v>855</v>
       </c>
     </row>
     <row r="42">
@@ -5401,7 +5489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5819,26 +5907,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>3.290739216204042</v>
+        <v>3.869958969082514</v>
       </c>
       <c r="D17" t="n">
-        <v>7592</v>
+        <v>9376</v>
       </c>
       <c r="E17" t="n">
-        <v>3.000367647058824</v>
+        <v>4.041544117647059</v>
       </c>
       <c r="F17" t="n">
         <v>96</v>
       </c>
       <c r="G17" t="n">
-        <v>0.290371569145218</v>
+        <v>-0.1715851485645454</v>
       </c>
     </row>
     <row r="18">
@@ -5848,22 +5936,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>3.33243209735256</v>
+        <v>3.290739216204042</v>
       </c>
       <c r="D18" t="n">
-        <v>6176</v>
+        <v>7592</v>
       </c>
       <c r="E18" t="n">
-        <v>3.263541666666667</v>
+        <v>3.000367647058824</v>
       </c>
       <c r="F18" t="n">
         <v>96</v>
       </c>
       <c r="G18" t="n">
-        <v>0.06889043068589285</v>
+        <v>0.290371569145218</v>
       </c>
     </row>
     <row r="19">
@@ -5873,22 +5961,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>3.536591102906034</v>
+        <v>3.33243209735256</v>
       </c>
       <c r="D19" t="n">
-        <v>6296</v>
+        <v>6176</v>
       </c>
       <c r="E19" t="n">
-        <v>3.466299019607843</v>
+        <v>3.263541666666667</v>
       </c>
       <c r="F19" t="n">
         <v>96</v>
       </c>
       <c r="G19" t="n">
-        <v>0.07029208329819125</v>
+        <v>0.06889043068589285</v>
       </c>
     </row>
     <row r="20">
@@ -5898,22 +5986,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>3.663854489164087</v>
+        <v>3.536591102906034</v>
       </c>
       <c r="D20" t="n">
-        <v>5176</v>
+        <v>6296</v>
       </c>
       <c r="E20" t="n">
-        <v>3.814889705882353</v>
+        <v>3.466299019607843</v>
       </c>
       <c r="F20" t="n">
         <v>96</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1510352167182663</v>
+        <v>0.07029208329819125</v>
       </c>
     </row>
     <row r="21">
@@ -5923,22 +6011,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>3.743944564470195</v>
+        <v>3.663854489164087</v>
       </c>
       <c r="D21" t="n">
-        <v>4800</v>
+        <v>5176</v>
       </c>
       <c r="E21" t="n">
-        <v>4.007598039215686</v>
+        <v>3.814889705882353</v>
       </c>
       <c r="F21" t="n">
         <v>96</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2636534747454911</v>
+        <v>-0.1510352167182663</v>
       </c>
     </row>
     <row r="22">
@@ -5948,22 +6036,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>3.776677555295115</v>
+        <v>3.743944564470195</v>
       </c>
       <c r="D22" t="n">
-        <v>4728</v>
+        <v>4800</v>
       </c>
       <c r="E22" t="n">
-        <v>4.014460784313726</v>
+        <v>4.007598039215686</v>
       </c>
       <c r="F22" t="n">
         <v>96</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.237783229018611</v>
+        <v>-0.2636534747454911</v>
       </c>
     </row>
     <row r="23">
@@ -5973,22 +6061,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>3.889255298078827</v>
+        <v>3.776677555295115</v>
       </c>
       <c r="D23" t="n">
-        <v>4168</v>
+        <v>4728</v>
       </c>
       <c r="E23" t="n">
-        <v>4.15392156862745</v>
+        <v>4.014460784313726</v>
       </c>
       <c r="F23" t="n">
         <v>96</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2646662705486231</v>
+        <v>-0.237783229018611</v>
       </c>
     </row>
     <row r="24">
@@ -5998,22 +6086,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>4.005326146015042</v>
+        <v>3.889255298078827</v>
       </c>
       <c r="D24" t="n">
-        <v>4136</v>
+        <v>4168</v>
       </c>
       <c r="E24" t="n">
-        <v>4.129044117647059</v>
+        <v>4.15392156862745</v>
       </c>
       <c r="F24" t="n">
         <v>96</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1237179716320167</v>
+        <v>-0.2646662705486231</v>
       </c>
     </row>
     <row r="25">
@@ -6023,22 +6111,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>3.999240719910011</v>
+        <v>4.005326146015042</v>
       </c>
       <c r="D25" t="n">
-        <v>3568</v>
+        <v>4136</v>
       </c>
       <c r="E25" t="n">
-        <v>4.220649509803922</v>
+        <v>4.129044117647059</v>
       </c>
       <c r="F25" t="n">
         <v>96</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2214087898939106</v>
+        <v>-0.1237179716320167</v>
       </c>
     </row>
     <row r="26">
@@ -6048,47 +6136,47 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" t="n">
-        <v>4.077670148096037</v>
+        <v>3.999240719910011</v>
       </c>
       <c r="D26" t="n">
-        <v>3280</v>
+        <v>3568</v>
       </c>
       <c r="E26" t="n">
-        <v>4.238419117647059</v>
+        <v>4.220649509803922</v>
       </c>
       <c r="F26" t="n">
         <v>96</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.1607489695510216</v>
+        <v>-0.2214087898939106</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C27" t="n">
-        <v>3.291063332476854</v>
+        <v>4.077670148096037</v>
       </c>
       <c r="D27" t="n">
-        <v>7120</v>
+        <v>3280</v>
       </c>
       <c r="E27" t="n">
-        <v>3.003247549019608</v>
+        <v>4.238419117647059</v>
       </c>
       <c r="F27" t="n">
         <v>96</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2878157834572463</v>
+        <v>-0.1607489695510216</v>
       </c>
     </row>
     <row r="28">
@@ -6098,22 +6186,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>3.473938140701307</v>
+        <v>3.291063332476854</v>
       </c>
       <c r="D28" t="n">
-        <v>6696</v>
+        <v>7120</v>
       </c>
       <c r="E28" t="n">
-        <v>3.180759803921569</v>
+        <v>3.003247549019608</v>
       </c>
       <c r="F28" t="n">
         <v>96</v>
       </c>
       <c r="G28" t="n">
-        <v>0.293178336779738</v>
+        <v>0.2878157834572463</v>
       </c>
     </row>
     <row r="29">
@@ -6123,22 +6211,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>3.559655103991918</v>
+        <v>3.473938140701307</v>
       </c>
       <c r="D29" t="n">
-        <v>6528</v>
+        <v>6696</v>
       </c>
       <c r="E29" t="n">
-        <v>3.308026960784314</v>
+        <v>3.180759803921569</v>
       </c>
       <c r="F29" t="n">
         <v>96</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2516281432076046</v>
+        <v>0.293178336779738</v>
       </c>
     </row>
     <row r="30">
@@ -6148,22 +6236,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>3.789291932327125</v>
+        <v>3.559655103991918</v>
       </c>
       <c r="D30" t="n">
-        <v>4904</v>
+        <v>6528</v>
       </c>
       <c r="E30" t="n">
-        <v>3.674203431372549</v>
+        <v>3.308026960784314</v>
       </c>
       <c r="F30" t="n">
         <v>96</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1150885009545761</v>
+        <v>0.2516281432076046</v>
       </c>
     </row>
     <row r="31">
@@ -6173,22 +6261,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>3.866575385749644</v>
+        <v>3.789291932327125</v>
       </c>
       <c r="D31" t="n">
-        <v>3744</v>
+        <v>4904</v>
       </c>
       <c r="E31" t="n">
-        <v>3.887990196078432</v>
+        <v>3.674203431372549</v>
       </c>
       <c r="F31" t="n">
         <v>96</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.02141481032878723</v>
+        <v>0.1150885009545761</v>
       </c>
     </row>
     <row r="32">
@@ -6198,22 +6286,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>3.927499916586033</v>
+        <v>3.866575385749644</v>
       </c>
       <c r="D32" t="n">
-        <v>5304</v>
+        <v>3744</v>
       </c>
       <c r="E32" t="n">
-        <v>4.016544117647059</v>
+        <v>3.887990196078432</v>
       </c>
       <c r="F32" t="n">
         <v>96</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.08904420106102551</v>
+        <v>-0.02141481032878723</v>
       </c>
     </row>
     <row r="33">
@@ -6223,22 +6311,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>3.996886296418009</v>
+        <v>3.927499916586033</v>
       </c>
       <c r="D33" t="n">
-        <v>6456</v>
+        <v>5304</v>
       </c>
       <c r="E33" t="n">
-        <v>3.897120098039216</v>
+        <v>4.016544117647059</v>
       </c>
       <c r="F33" t="n">
         <v>96</v>
       </c>
       <c r="G33" t="n">
-        <v>0.09976619837879319</v>
+        <v>-0.08904420106102551</v>
       </c>
     </row>
     <row r="34">
@@ -6248,22 +6336,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>4.173726067180183</v>
+        <v>3.996886296418009</v>
       </c>
       <c r="D34" t="n">
-        <v>6136</v>
+        <v>6456</v>
       </c>
       <c r="E34" t="n">
-        <v>4.085416666666666</v>
+        <v>3.897120098039216</v>
       </c>
       <c r="F34" t="n">
         <v>96</v>
       </c>
       <c r="G34" t="n">
-        <v>0.08830940051351632</v>
+        <v>0.09976619837879319</v>
       </c>
     </row>
     <row r="35">
@@ -6273,22 +6361,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C35" t="n">
-        <v>4.104804034498446</v>
+        <v>4.173726067180183</v>
       </c>
       <c r="D35" t="n">
-        <v>6088</v>
+        <v>6136</v>
       </c>
       <c r="E35" t="n">
-        <v>4.143872549019608</v>
+        <v>4.085416666666666</v>
       </c>
       <c r="F35" t="n">
         <v>96</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.03906851452116111</v>
+        <v>0.08830940051351632</v>
       </c>
     </row>
     <row r="36">
@@ -6298,21 +6386,46 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C36" t="n">
-        <v>4.320434945333217</v>
+        <v>4.104804034498446</v>
       </c>
       <c r="D36" t="n">
-        <v>7408</v>
+        <v>6088</v>
       </c>
       <c r="E36" t="n">
-        <v>4.19718137254902</v>
+        <v>4.143872549019608</v>
       </c>
       <c r="F36" t="n">
         <v>96</v>
       </c>
       <c r="G36" t="n">
+        <v>-0.03906851452116111</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>9</v>
+      </c>
+      <c r="C37" t="n">
+        <v>4.320434945333217</v>
+      </c>
+      <c r="D37" t="n">
+        <v>7408</v>
+      </c>
+      <c r="E37" t="n">
+        <v>4.19718137254902</v>
+      </c>
+      <c r="F37" t="n">
+        <v>96</v>
+      </c>
+      <c r="G37" t="n">
         <v>0.123253572784197</v>
       </c>
     </row>

--- a/Exp3_PTO_GRPO/eda/results/arms/training/tables/gpt-4o-mini/training.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/training/tables/gpt-4o-mini/training.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1053,34 +1053,34 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>7574</v>
+        <v>9248</v>
       </c>
       <c r="E18" t="n">
-        <v>3.290739216204042</v>
+        <v>4.112989772033381</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8046651305316942</v>
+        <v>0.7511871813615815</v>
       </c>
       <c r="G18" t="n">
-        <v>2.352941176470588</v>
+        <v>2.847058823529411</v>
       </c>
       <c r="H18" t="n">
-        <v>3.311764705882353</v>
+        <v>4.376470588235295</v>
       </c>
       <c r="I18" t="n">
-        <v>4.435294117647059</v>
+        <v>4.911764705882353</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1089,37 +1089,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>6168</v>
+        <v>14800</v>
       </c>
       <c r="E19" t="n">
-        <v>3.33243209735256</v>
+        <v>4.093557233704293</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7666601470607851</v>
+        <v>0.7821904294093468</v>
       </c>
       <c r="G19" t="n">
-        <v>2.302352941176471</v>
+        <v>2.847058823529411</v>
       </c>
       <c r="H19" t="n">
-        <v>3.435294117647059</v>
+        <v>4.376470588235295</v>
       </c>
       <c r="I19" t="n">
-        <v>4.405882352941177</v>
+        <v>4.911764705882353</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.02027027027027027</v>
       </c>
     </row>
     <row r="20">
@@ -1134,25 +1134,25 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>6277</v>
+        <v>7574</v>
       </c>
       <c r="E20" t="n">
-        <v>3.536591102906034</v>
+        <v>3.290739216204042</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6748374152512981</v>
+        <v>0.8046651305316942</v>
       </c>
       <c r="G20" t="n">
-        <v>2.647058823529412</v>
+        <v>2.352941176470588</v>
       </c>
       <c r="H20" t="n">
-        <v>3.470588235294118</v>
+        <v>3.311764705882353</v>
       </c>
       <c r="I20" t="n">
-        <v>4.476470588235294</v>
+        <v>4.435294117647059</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1170,22 +1170,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>5168</v>
+        <v>6168</v>
       </c>
       <c r="E21" t="n">
-        <v>3.663854489164087</v>
+        <v>3.33243209735256</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5430193468825506</v>
+        <v>0.7666601470607851</v>
       </c>
       <c r="G21" t="n">
-        <v>2.91764705882353</v>
+        <v>2.302352941176471</v>
       </c>
       <c r="H21" t="n">
-        <v>3.670588235294118</v>
+        <v>3.435294117647059</v>
       </c>
       <c r="I21" t="n">
         <v>4.405882352941177</v>
@@ -1206,25 +1206,25 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>4792</v>
+        <v>6277</v>
       </c>
       <c r="E22" t="n">
-        <v>3.743944564470195</v>
+        <v>3.536591102906034</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5762331485203405</v>
+        <v>0.6748374152512981</v>
       </c>
       <c r="G22" t="n">
-        <v>2.976470588235294</v>
+        <v>2.647058823529412</v>
       </c>
       <c r="H22" t="n">
-        <v>3.7</v>
+        <v>3.470588235294118</v>
       </c>
       <c r="I22" t="n">
-        <v>4.564705882352941</v>
+        <v>4.476470588235294</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1242,25 +1242,25 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>4718</v>
+        <v>5168</v>
       </c>
       <c r="E23" t="n">
-        <v>3.776677555295115</v>
+        <v>3.663854489164087</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5295341015127092</v>
+        <v>0.5430193468825506</v>
       </c>
       <c r="G23" t="n">
-        <v>3.076470588235294</v>
+        <v>2.91764705882353</v>
       </c>
       <c r="H23" t="n">
-        <v>3.735294117647059</v>
+        <v>3.670588235294118</v>
       </c>
       <c r="I23" t="n">
-        <v>4.552941176470588</v>
+        <v>4.405882352941177</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>4158</v>
+        <v>4792</v>
       </c>
       <c r="E24" t="n">
-        <v>3.889255298078827</v>
+        <v>3.743944564470195</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5741195003775807</v>
+        <v>0.5762331485203405</v>
       </c>
       <c r="G24" t="n">
-        <v>3.111764705882353</v>
+        <v>2.976470588235294</v>
       </c>
       <c r="H24" t="n">
-        <v>3.858823529411764</v>
+        <v>3.7</v>
       </c>
       <c r="I24" t="n">
-        <v>4.623529411764705</v>
+        <v>4.564705882352941</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1314,25 +1314,25 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>4114</v>
+        <v>4718</v>
       </c>
       <c r="E25" t="n">
-        <v>4.005326146015042</v>
+        <v>3.776677555295115</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5416210462718096</v>
+        <v>0.5295341015127092</v>
       </c>
       <c r="G25" t="n">
-        <v>3.370588235294118</v>
+        <v>3.076470588235294</v>
       </c>
       <c r="H25" t="n">
-        <v>3.858823529411764</v>
+        <v>3.735294117647059</v>
       </c>
       <c r="I25" t="n">
-        <v>4.823529411764707</v>
+        <v>4.552941176470588</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1350,25 +1350,25 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>3556</v>
+        <v>4158</v>
       </c>
       <c r="E26" t="n">
-        <v>3.999240719910011</v>
+        <v>3.889255298078827</v>
       </c>
       <c r="F26" t="n">
-        <v>0.513138129373051</v>
+        <v>0.5741195003775807</v>
       </c>
       <c r="G26" t="n">
-        <v>3.391176470588235</v>
+        <v>3.111764705882353</v>
       </c>
       <c r="H26" t="n">
-        <v>3.947058823529412</v>
+        <v>3.858823529411764</v>
       </c>
       <c r="I26" t="n">
-        <v>4.852941176470589</v>
+        <v>4.623529411764705</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1386,25 +1386,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>3261</v>
+        <v>4114</v>
       </c>
       <c r="E27" t="n">
-        <v>4.077670148096037</v>
+        <v>4.005326146015042</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5552196216842494</v>
+        <v>0.5416210462718096</v>
       </c>
       <c r="G27" t="n">
-        <v>3.329411764705882</v>
+        <v>3.370588235294118</v>
       </c>
       <c r="H27" t="n">
-        <v>4.117647058823529</v>
+        <v>3.858823529411764</v>
       </c>
       <c r="I27" t="n">
-        <v>4.852941176470589</v>
+        <v>4.823529411764707</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1422,25 +1422,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>7097</v>
+        <v>3556</v>
       </c>
       <c r="E28" t="n">
-        <v>3.291063332476854</v>
+        <v>3.999240719910011</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9647864799567627</v>
+        <v>0.513138129373051</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>3.391176470588235</v>
       </c>
       <c r="H28" t="n">
-        <v>3.435294117647059</v>
+        <v>3.947058823529412</v>
       </c>
       <c r="I28" t="n">
-        <v>4.535294117647059</v>
+        <v>4.852941176470589</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1458,25 +1458,25 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>6685</v>
+        <v>3261</v>
       </c>
       <c r="E29" t="n">
-        <v>3.473938140701307</v>
+        <v>4.077670148096037</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8816031388249556</v>
+        <v>0.5552196216842494</v>
       </c>
       <c r="G29" t="n">
-        <v>2.310588235294118</v>
+        <v>3.329411764705882</v>
       </c>
       <c r="H29" t="n">
-        <v>3.505882352941176</v>
+        <v>4.117647058823529</v>
       </c>
       <c r="I29" t="n">
-        <v>4.564705882352941</v>
+        <v>4.852941176470589</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1494,25 +1494,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>6522</v>
+        <v>7097</v>
       </c>
       <c r="E30" t="n">
-        <v>3.559655103991918</v>
+        <v>3.291063332476854</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8483398044383608</v>
+        <v>0.9647864799567627</v>
       </c>
       <c r="G30" t="n">
-        <v>2.382352941176471</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>3.623529411764706</v>
+        <v>3.435294117647059</v>
       </c>
       <c r="I30" t="n">
-        <v>4.594117647058823</v>
+        <v>4.535294117647059</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1530,25 +1530,25 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>4899</v>
+        <v>6685</v>
       </c>
       <c r="E31" t="n">
-        <v>3.789291932327125</v>
+        <v>3.473938140701307</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7231635892705964</v>
+        <v>0.8816031388249556</v>
       </c>
       <c r="G31" t="n">
-        <v>2.758823529411765</v>
+        <v>2.310588235294118</v>
       </c>
       <c r="H31" t="n">
-        <v>3.841176470588235</v>
+        <v>3.505882352941176</v>
       </c>
       <c r="I31" t="n">
-        <v>4.652941176470588</v>
+        <v>4.564705882352941</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1566,25 +1566,25 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>3351</v>
+        <v>6522</v>
       </c>
       <c r="E32" t="n">
-        <v>3.866575385749644</v>
+        <v>3.559655103991918</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7382916147127863</v>
+        <v>0.8483398044383608</v>
       </c>
       <c r="G32" t="n">
-        <v>2.817647058823529</v>
+        <v>2.382352941176471</v>
       </c>
       <c r="H32" t="n">
-        <v>3.982352941176471</v>
+        <v>3.623529411764706</v>
       </c>
       <c r="I32" t="n">
-        <v>4.794117647058823</v>
+        <v>4.594117647058823</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1602,25 +1602,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>5289</v>
+        <v>4899</v>
       </c>
       <c r="E33" t="n">
-        <v>3.927499916586033</v>
+        <v>3.789291932327125</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7053329596308401</v>
+        <v>0.7231635892705964</v>
       </c>
       <c r="G33" t="n">
-        <v>2.817647058823529</v>
+        <v>2.758823529411765</v>
       </c>
       <c r="H33" t="n">
-        <v>4.076470588235294</v>
+        <v>3.841176470588235</v>
       </c>
       <c r="I33" t="n">
-        <v>4.794117647058823</v>
+        <v>4.652941176470588</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1638,25 +1638,25 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>6444</v>
+        <v>3351</v>
       </c>
       <c r="E34" t="n">
-        <v>3.996886296418009</v>
+        <v>3.866575385749644</v>
       </c>
       <c r="F34" t="n">
-        <v>0.699194486280059</v>
+        <v>0.7382916147127863</v>
       </c>
       <c r="G34" t="n">
-        <v>2.847058823529411</v>
+        <v>2.817647058823529</v>
       </c>
       <c r="H34" t="n">
-        <v>4.158823529411764</v>
+        <v>3.982352941176471</v>
       </c>
       <c r="I34" t="n">
-        <v>4.882352941176471</v>
+        <v>4.794117647058823</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1674,25 +1674,25 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>6117</v>
+        <v>5289</v>
       </c>
       <c r="E35" t="n">
-        <v>4.173726067180183</v>
+        <v>3.927499916586033</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7248460576901864</v>
+        <v>0.7053329596308401</v>
       </c>
       <c r="G35" t="n">
         <v>2.817647058823529</v>
       </c>
       <c r="H35" t="n">
-        <v>4.376470588235295</v>
+        <v>4.076470588235294</v>
       </c>
       <c r="I35" t="n">
-        <v>4.911764705882353</v>
+        <v>4.794117647058823</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1710,25 +1710,25 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D36" t="n">
-        <v>6077</v>
+        <v>6444</v>
       </c>
       <c r="E36" t="n">
-        <v>4.104804034498446</v>
+        <v>3.996886296418009</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6493581191361258</v>
+        <v>0.699194486280059</v>
       </c>
       <c r="G36" t="n">
-        <v>2.947058823529412</v>
+        <v>2.847058823529411</v>
       </c>
       <c r="H36" t="n">
-        <v>4.276470588235294</v>
+        <v>4.158823529411764</v>
       </c>
       <c r="I36" t="n">
-        <v>4.852941176470589</v>
+        <v>4.882352941176471</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1746,27 +1746,99 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D37" t="n">
-        <v>7387</v>
+        <v>6117</v>
       </c>
       <c r="E37" t="n">
-        <v>4.320434945333217</v>
+        <v>4.173726067180183</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6017010582352287</v>
+        <v>0.7248460576901864</v>
       </c>
       <c r="G37" t="n">
-        <v>3.441176470588236</v>
+        <v>2.817647058823529</v>
       </c>
       <c r="H37" t="n">
-        <v>4.464705882352941</v>
+        <v>4.376470588235295</v>
       </c>
       <c r="I37" t="n">
         <v>4.911764705882353</v>
       </c>
       <c r="J37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>9</v>
+      </c>
+      <c r="D38" t="n">
+        <v>6077</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4.104804034498446</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.6493581191361258</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.947058823529412</v>
+      </c>
+      <c r="H38" t="n">
+        <v>4.276470588235294</v>
+      </c>
+      <c r="I38" t="n">
+        <v>4.852941176470589</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>10</v>
+      </c>
+      <c r="D39" t="n">
+        <v>7387</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4.320434945333217</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.6017010582352287</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3.441176470588236</v>
+      </c>
+      <c r="H39" t="n">
+        <v>4.464705882352941</v>
+      </c>
+      <c r="I39" t="n">
+        <v>4.911764705882353</v>
+      </c>
+      <c r="J39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1781,7 +1853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2218,55 +2290,49 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.104477462659227</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2735077171015929</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.3217316082443207</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.2764705882352937</v>
-      </c>
-      <c r="I18" t="n">
-        <v>782</v>
+        <v>0.3105739873804193</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.05276816608996539</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.1137702512594409</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2502057299603779</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.2988387588044927</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.2588235294117647</v>
-      </c>
-      <c r="I19" t="n">
-        <v>618</v>
+        <v>0.3394817170111288</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.06432432432432432</v>
       </c>
     </row>
     <row r="20">
@@ -2281,19 +2347,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.24403916585694</v>
+        <v>0.2735077171015929</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2945635673624288</v>
+        <v>0.3217316082443207</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2588235294117647</v>
+        <v>0.2764705882352937</v>
       </c>
       <c r="I20" t="n">
-        <v>620</v>
+        <v>782</v>
       </c>
     </row>
     <row r="21">
@@ -2308,19 +2374,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2317847077007</v>
+        <v>0.2502057299603779</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2689969271290605</v>
+        <v>0.2988387588044927</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2352941176470589</v>
+        <v>0.2588235294117647</v>
       </c>
       <c r="I21" t="n">
-        <v>536</v>
+        <v>618</v>
       </c>
     </row>
     <row r="22">
@@ -2335,19 +2401,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2366862745098039</v>
+        <v>0.24403916585694</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2812324929971988</v>
+        <v>0.2945635673624288</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2470588235294118</v>
+        <v>0.2588235294117647</v>
       </c>
       <c r="I22" t="n">
-        <v>483</v>
+        <v>620</v>
       </c>
     </row>
     <row r="23">
@@ -2362,19 +2428,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2253110381208321</v>
+        <v>0.2317847077007</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2672693498452013</v>
+        <v>0.2689969271290605</v>
       </c>
       <c r="H23" t="n">
         <v>0.2352941176470589</v>
       </c>
       <c r="I23" t="n">
-        <v>475</v>
+        <v>536</v>
       </c>
     </row>
     <row r="24">
@@ -2389,19 +2455,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2201648413684092</v>
+        <v>0.2366862745098039</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2718382352941177</v>
+        <v>0.2812324929971988</v>
       </c>
       <c r="H24" t="n">
         <v>0.2470588235294118</v>
       </c>
       <c r="I24" t="n">
-        <v>400</v>
+        <v>483</v>
       </c>
     </row>
     <row r="25">
@@ -2416,19 +2482,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>0.195312322220958</v>
+        <v>0.2253110381208321</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2490765171503958</v>
+        <v>0.2672693498452013</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2294117647058824</v>
+        <v>0.2352941176470589</v>
       </c>
       <c r="I25" t="n">
-        <v>379</v>
+        <v>475</v>
       </c>
     </row>
     <row r="26">
@@ -2443,19 +2509,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2253363228699552</v>
+        <v>0.2201648413684092</v>
       </c>
       <c r="G26" t="n">
-        <v>0.265716147955027</v>
+        <v>0.2718382352941177</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2470588235294109</v>
+        <v>0.2470588235294118</v>
       </c>
       <c r="I26" t="n">
-        <v>361</v>
+        <v>400</v>
       </c>
     </row>
     <row r="27">
@@ -2470,25 +2536,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1957532281205165</v>
+        <v>0.195312322220958</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2667364454678668</v>
+        <v>0.2490765171503958</v>
       </c>
       <c r="H27" t="n">
         <v>0.2294117647058824</v>
       </c>
       <c r="I27" t="n">
-        <v>281</v>
+        <v>379</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2497,25 +2563,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4241705221414408</v>
+        <v>0.2253363228699552</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4512302036199095</v>
+        <v>0.265716147955027</v>
       </c>
       <c r="H28" t="n">
-        <v>0.391176470588235</v>
+        <v>0.2470588235294109</v>
       </c>
       <c r="I28" t="n">
-        <v>832</v>
+        <v>361</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2524,19 +2590,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
-        <v>0.431745027760208</v>
+        <v>0.1957532281205165</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4614169060940571</v>
+        <v>0.2667364454678668</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4058823529411766</v>
+        <v>0.2294117647058824</v>
       </c>
       <c r="I29" t="n">
-        <v>778</v>
+        <v>281</v>
       </c>
     </row>
     <row r="30">
@@ -2551,19 +2617,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4447303921568627</v>
+        <v>0.4241705221414408</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4704503676470588</v>
+        <v>0.4512302036199095</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3970588235294117</v>
+        <v>0.391176470588235</v>
       </c>
       <c r="I30" t="n">
-        <v>768</v>
+        <v>832</v>
       </c>
     </row>
     <row r="31">
@@ -2578,19 +2644,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>0.396497457057864</v>
+        <v>0.431745027760208</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4260474349597744</v>
+        <v>0.4614169060940571</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3588235294117643</v>
+        <v>0.4058823529411766</v>
       </c>
       <c r="I31" t="n">
-        <v>563</v>
+        <v>778</v>
       </c>
     </row>
     <row r="32">
@@ -2605,19 +2671,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3809829059829061</v>
+        <v>0.4447303921568627</v>
       </c>
       <c r="G32" t="n">
-        <v>0.408632897603486</v>
+        <v>0.4704503676470588</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3529411764705881</v>
+        <v>0.3970588235294117</v>
       </c>
       <c r="I32" t="n">
-        <v>432</v>
+        <v>768</v>
       </c>
     </row>
     <row r="33">
@@ -2632,19 +2698,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3324017389761335</v>
+        <v>0.396497457057864</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3789560894780448</v>
+        <v>0.4260474349597744</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3235294117647058</v>
+        <v>0.3588235294117643</v>
       </c>
       <c r="I33" t="n">
-        <v>568</v>
+        <v>563</v>
       </c>
     </row>
     <row r="34">
@@ -2659,19 +2725,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3317515853925214</v>
+        <v>0.3809829059829061</v>
       </c>
       <c r="G34" t="n">
-        <v>0.381601639204303</v>
+        <v>0.408632897603486</v>
       </c>
       <c r="H34" t="n">
-        <v>0.3352941176470585</v>
+        <v>0.3529411764705881</v>
       </c>
       <c r="I34" t="n">
-        <v>689</v>
+        <v>432</v>
       </c>
     </row>
     <row r="35">
@@ -2686,19 +2752,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2731497814249559</v>
+        <v>0.3324017389761335</v>
       </c>
       <c r="G35" t="n">
-        <v>0.3538677771993754</v>
+        <v>0.3789560894780448</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2588235294117656</v>
+        <v>0.3235294117647058</v>
       </c>
       <c r="I35" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
     </row>
     <row r="36">
@@ -2713,19 +2779,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3020483883435108</v>
+        <v>0.3317515853925214</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3677736657576938</v>
+        <v>0.381601639204303</v>
       </c>
       <c r="H36" t="n">
-        <v>0.276470588235294</v>
+        <v>0.3352941176470585</v>
       </c>
       <c r="I36" t="n">
-        <v>604</v>
+        <v>689</v>
       </c>
     </row>
     <row r="37">
@@ -2740,18 +2806,72 @@
         </is>
       </c>
       <c r="C37" t="n">
+        <v>8</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.2731497814249559</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.3538677771993754</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2588235294117656</v>
+      </c>
+      <c r="I37" t="n">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>9</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.3020483883435108</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.3677736657576938</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.276470588235294</v>
+      </c>
+      <c r="I38" t="n">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
         <v>10</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E39" t="n">
         <v>0.2335662558760005</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G39" t="n">
         <v>0.3282486414338833</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H39" t="n">
         <v>0.2352941176470589</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I39" t="n">
         <v>617</v>
       </c>
     </row>
@@ -2766,7 +2886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3262,57 +3382,57 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>7592</v>
+        <v>9248</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>3.290739216204042</v>
+        <v>4.112989772033381</v>
       </c>
       <c r="H18" t="n">
-        <v>286.2219441517387</v>
+        <v>870.2514057093425</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>6176</v>
+        <v>14800</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.13</v>
+        <v>0.02</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="G19" t="n">
-        <v>3.33243209735256</v>
+        <v>4.093557233704293</v>
       </c>
       <c r="H19" t="n">
-        <v>324.7984132124352</v>
+        <v>947.6527702702703</v>
       </c>
     </row>
     <row r="20">
@@ -3322,25 +3442,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>6296</v>
+        <v>7592</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>3.536591102906034</v>
+        <v>3.290739216204042</v>
       </c>
       <c r="H20" t="n">
-        <v>345.3122617534943</v>
+        <v>286.2219441517387</v>
       </c>
     </row>
     <row r="21">
@@ -3350,25 +3470,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>5176</v>
+        <v>6176</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>3.663854489164087</v>
+        <v>3.33243209735256</v>
       </c>
       <c r="H21" t="n">
-        <v>398.2600463678516</v>
+        <v>324.7984132124352</v>
       </c>
     </row>
     <row r="22">
@@ -3378,25 +3498,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>4800</v>
+        <v>6296</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.17</v>
+        <v>0.3</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>3.743944564470195</v>
+        <v>3.536591102906034</v>
       </c>
       <c r="H22" t="n">
-        <v>534.891875</v>
+        <v>345.3122617534943</v>
       </c>
     </row>
     <row r="23">
@@ -3406,25 +3526,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>4728</v>
+        <v>5176</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>3.776677555295115</v>
+        <v>3.663854489164087</v>
       </c>
       <c r="H23" t="n">
-        <v>609.8616751269036</v>
+        <v>398.2600463678516</v>
       </c>
     </row>
     <row r="24">
@@ -3434,25 +3554,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>4168</v>
+        <v>4800</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>3.889255298078827</v>
+        <v>3.743944564470195</v>
       </c>
       <c r="H24" t="n">
-        <v>740.5856525911709</v>
+        <v>534.891875</v>
       </c>
     </row>
     <row r="25">
@@ -3462,25 +3582,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>4136</v>
+        <v>4728</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.53</v>
+        <v>0.21</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>4.005326146015042</v>
+        <v>3.776677555295115</v>
       </c>
       <c r="H25" t="n">
-        <v>697.2487911025145</v>
+        <v>609.8616751269036</v>
       </c>
     </row>
     <row r="26">
@@ -3490,25 +3610,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>3568</v>
+        <v>4168</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.34</v>
+        <v>0.24</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>3.999240719910011</v>
+        <v>3.889255298078827</v>
       </c>
       <c r="H26" t="n">
-        <v>808.7051569506726</v>
+        <v>740.5856525911709</v>
       </c>
     </row>
     <row r="27">
@@ -3518,81 +3638,81 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C27" t="n">
-        <v>3280</v>
+        <v>4136</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>4.077670148096037</v>
+        <v>4.005326146015042</v>
       </c>
       <c r="H27" t="n">
-        <v>829.6390243902439</v>
+        <v>697.2487911025145</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C28" t="n">
-        <v>7120</v>
+        <v>3568</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>3.291063332476854</v>
+        <v>3.999240719910011</v>
       </c>
       <c r="H28" t="n">
-        <v>305.6846910112359</v>
+        <v>808.7051569506726</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C29" t="n">
-        <v>6696</v>
+        <v>3280</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.16</v>
+        <v>0.58</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>3.473938140701307</v>
+        <v>4.077670148096037</v>
       </c>
       <c r="H29" t="n">
-        <v>363.8626045400239</v>
+        <v>829.6390243902439</v>
       </c>
     </row>
     <row r="30">
@@ -3602,25 +3722,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>6528</v>
+        <v>7120</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.09</v>
+        <v>0.32</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>3.559655103991918</v>
+        <v>3.291063332476854</v>
       </c>
       <c r="H30" t="n">
-        <v>445.0816482843137</v>
+        <v>305.6846910112359</v>
       </c>
     </row>
     <row r="31">
@@ -3630,25 +3750,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>4904</v>
+        <v>6696</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>3.789291932327125</v>
+        <v>3.473938140701307</v>
       </c>
       <c r="H31" t="n">
-        <v>561.2230831973899</v>
+        <v>363.8626045400239</v>
       </c>
     </row>
     <row r="32">
@@ -3658,25 +3778,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>3744</v>
+        <v>6528</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>3.866575385749644</v>
+        <v>3.559655103991918</v>
       </c>
       <c r="H32" t="n">
-        <v>632.4281517094017</v>
+        <v>445.0816482843137</v>
       </c>
     </row>
     <row r="33">
@@ -3686,25 +3806,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>5304</v>
+        <v>4904</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0.28</v>
+        <v>0.1</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>3.927499916586033</v>
+        <v>3.789291932327125</v>
       </c>
       <c r="H33" t="n">
-        <v>752.7567873303168</v>
+        <v>561.2230831973899</v>
       </c>
     </row>
     <row r="34">
@@ -3714,25 +3834,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>6456</v>
+        <v>3744</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>3.996886296418009</v>
+        <v>3.866575385749644</v>
       </c>
       <c r="H34" t="n">
-        <v>836.0020136307311</v>
+        <v>632.4281517094017</v>
       </c>
     </row>
     <row r="35">
@@ -3742,25 +3862,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>6136</v>
+        <v>5304</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>4.173726067180183</v>
+        <v>3.927499916586033</v>
       </c>
       <c r="H35" t="n">
-        <v>936.5017926988266</v>
+        <v>752.7567873303168</v>
       </c>
     </row>
     <row r="36">
@@ -3770,25 +3890,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C36" t="n">
-        <v>6088</v>
+        <v>6456</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>4.104804034498446</v>
+        <v>3.996886296418009</v>
       </c>
       <c r="H36" t="n">
-        <v>960.3909329829172</v>
+        <v>836.0020136307311</v>
       </c>
     </row>
     <row r="37">
@@ -3798,24 +3918,80 @@
         </is>
       </c>
       <c r="B37" t="n">
+        <v>8</v>
+      </c>
+      <c r="C37" t="n">
+        <v>6136</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>4.173726067180183</v>
+      </c>
+      <c r="H37" t="n">
+        <v>936.5017926988266</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>9</v>
+      </c>
+      <c r="C38" t="n">
+        <v>6088</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4.104804034498446</v>
+      </c>
+      <c r="H38" t="n">
+        <v>960.3909329829172</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
         <v>10</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C39" t="n">
         <v>7408</v>
       </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
         <v>0.28</v>
       </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
         <v>4.320434945333217</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H39" t="n">
         <v>1003.434260259179</v>
       </c>
     </row>
@@ -3868,7 +4044,7 @@
         <v>0.8599</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8743</v>
+        <v>0.876</v>
       </c>
       <c r="D2" t="n">
         <v>0.8647</v>
@@ -3885,7 +4061,7 @@
         <v>0.872</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8922</v>
+        <v>0.8944</v>
       </c>
       <c r="D3" t="n">
         <v>0.8633999999999999</v>
@@ -3902,7 +4078,7 @@
         <v>0.8781</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8989</v>
+        <v>0.9006999999999999</v>
       </c>
       <c r="D4" t="n">
         <v>0.8577</v>
@@ -3919,7 +4095,7 @@
         <v>0.8758</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8994</v>
+        <v>0.9026</v>
       </c>
       <c r="D5" t="n">
         <v>0.8413</v>
@@ -3936,7 +4112,7 @@
         <v>0.8738</v>
       </c>
       <c r="C6" t="n">
-        <v>0.896</v>
+        <v>0.9021</v>
       </c>
       <c r="D6" t="n">
         <v>0.8247</v>
@@ -3953,7 +4129,7 @@
         <v>0.8768</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8932</v>
+        <v>0.9026999999999999</v>
       </c>
       <c r="D7" t="n">
         <v>0.8084</v>
@@ -3970,7 +4146,7 @@
         <v>0.8754</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.9035</v>
       </c>
       <c r="D8" t="n">
         <v>0.7887999999999999</v>
@@ -3987,7 +4163,7 @@
         <v>0.8739</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9013</v>
+        <v>0.9086</v>
       </c>
       <c r="D9" t="n">
         <v>0.7868000000000001</v>
@@ -4004,7 +4180,7 @@
         <v>0.8672</v>
       </c>
       <c r="C10" t="n">
-        <v>0.895</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="D10" t="n">
         <v>0.7837</v>
@@ -4021,7 +4197,7 @@
         <v>0.8738</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8982</v>
+        <v>0.9066</v>
       </c>
       <c r="D11" t="n">
         <v>0.7637</v>
@@ -4038,7 +4214,7 @@
         <v>0.8663</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8991</v>
+        <v>0.908</v>
       </c>
       <c r="D12" t="n">
         <v>0.7633</v>
@@ -4055,7 +4231,7 @@
         <v>0.8737</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9005</v>
+        <v>0.9084</v>
       </c>
       <c r="D13" t="n">
         <v>0.7597</v>
@@ -4072,7 +4248,7 @@
         <v>0.8759</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9058</v>
+        <v>0.9111</v>
       </c>
       <c r="D14" t="n">
         <v>0.7668</v>
@@ -4089,7 +4265,7 @@
         <v>0.8725000000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9145</v>
+        <v>0.9169</v>
       </c>
       <c r="D15" t="n">
         <v>0.7654</v>
@@ -4106,7 +4282,7 @@
         <v>0.8822</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9258</v>
+        <v>0.929</v>
       </c>
       <c r="D16" t="n">
         <v>0.7581</v>
@@ -4123,7 +4299,7 @@
         <v>0.8842</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9254</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="D17" t="n">
         <v>0.7376</v>
@@ -4140,7 +4316,7 @@
         <v>0.8744</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9194</v>
+        <v>0.9284</v>
       </c>
       <c r="D18" t="n">
         <v>0.7478</v>
@@ -4157,7 +4333,7 @@
         <v>0.8815</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9223</v>
+        <v>0.9281</v>
       </c>
       <c r="D19" t="n">
         <v>0.7574</v>
@@ -4174,7 +4350,7 @@
         <v>0.8925999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9304</v>
+        <v>0.9363</v>
       </c>
       <c r="D20" t="n">
         <v>0.7561</v>
@@ -4191,7 +4367,7 @@
         <v>0.8968</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9357</v>
+        <v>0.9418</v>
       </c>
     </row>
   </sheetData>
@@ -4560,10 +4736,10 @@
         <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8743062220923924</v>
+        <v>0.875998003992016</v>
       </c>
       <c r="D22" t="n">
-        <v>23963</v>
+        <v>28056</v>
       </c>
     </row>
     <row r="23">
@@ -4576,10 +4752,10 @@
         <v>14</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8922375641706497</v>
+        <v>0.8943778732383751</v>
       </c>
       <c r="D23" t="n">
-        <v>22596</v>
+        <v>26538</v>
       </c>
     </row>
     <row r="24">
@@ -4592,10 +4768,10 @@
         <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8989062961868164</v>
+        <v>0.9006824636513925</v>
       </c>
       <c r="D24" t="n">
-        <v>20298</v>
+        <v>23591</v>
       </c>
     </row>
     <row r="25">
@@ -4608,10 +4784,10 @@
         <v>18</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8994314360824112</v>
+        <v>0.9026370217166494</v>
       </c>
       <c r="D25" t="n">
-        <v>16357</v>
+        <v>19340</v>
       </c>
     </row>
     <row r="26">
@@ -4624,10 +4800,10 @@
         <v>20</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8959875340864822</v>
+        <v>0.9020856344616984</v>
       </c>
       <c r="D26" t="n">
-        <v>12835</v>
+        <v>15391</v>
       </c>
     </row>
     <row r="27">
@@ -4640,10 +4816,10 @@
         <v>22</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8932208620512293</v>
+        <v>0.9027194896760115</v>
       </c>
       <c r="D27" t="n">
-        <v>9721</v>
+        <v>11914</v>
       </c>
     </row>
     <row r="28">
@@ -4656,10 +4832,10 @@
         <v>24</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8946927374301676</v>
+        <v>0.9034546934977318</v>
       </c>
       <c r="D28" t="n">
-        <v>7160</v>
+        <v>8597</v>
       </c>
     </row>
     <row r="29">
@@ -4672,10 +4848,10 @@
         <v>26</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9012704174228675</v>
+        <v>0.9085868424996254</v>
       </c>
       <c r="D29" t="n">
-        <v>5510</v>
+        <v>6673</v>
       </c>
     </row>
     <row r="30">
@@ -4688,10 +4864,10 @@
         <v>28</v>
       </c>
       <c r="C30" t="n">
-        <v>0.894954327968682</v>
+        <v>0.9047185279650209</v>
       </c>
       <c r="D30" t="n">
-        <v>4598</v>
+        <v>5489</v>
       </c>
     </row>
     <row r="31">
@@ -4704,10 +4880,10 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8982202447163515</v>
+        <v>0.9065662508825606</v>
       </c>
       <c r="D31" t="n">
-        <v>3596</v>
+        <v>4249</v>
       </c>
     </row>
     <row r="32">
@@ -4720,10 +4896,10 @@
         <v>32</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8990997749437359</v>
+        <v>0.908005164622337</v>
       </c>
       <c r="D32" t="n">
-        <v>2666</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="33">
@@ -4736,10 +4912,10 @@
         <v>34</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9005210800568451</v>
+        <v>0.9083747927031509</v>
       </c>
       <c r="D33" t="n">
-        <v>2111</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="34">
@@ -4752,10 +4928,10 @@
         <v>36</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9057619816908993</v>
+        <v>0.9111006585136406</v>
       </c>
       <c r="D34" t="n">
-        <v>1857</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="35">
@@ -4768,10 +4944,10 @@
         <v>38</v>
       </c>
       <c r="C35" t="n">
-        <v>0.9145183175033921</v>
+        <v>0.9168646080760094</v>
       </c>
       <c r="D35" t="n">
-        <v>1474</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="36">
@@ -4784,10 +4960,10 @@
         <v>40</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9258137774413323</v>
+        <v>0.92904953145917</v>
       </c>
       <c r="D36" t="n">
-        <v>1321</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="37">
@@ -4800,10 +4976,10 @@
         <v>42</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9253981559094719</v>
+        <v>0.9298507462686567</v>
       </c>
       <c r="D37" t="n">
-        <v>1193</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="38">
@@ -4816,10 +4992,10 @@
         <v>44</v>
       </c>
       <c r="C38" t="n">
-        <v>0.9193697868396663</v>
+        <v>0.9283970707892596</v>
       </c>
       <c r="D38" t="n">
-        <v>1079</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="39">
@@ -4832,10 +5008,10 @@
         <v>46</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9223007063572149</v>
+        <v>0.9280701754385965</v>
       </c>
       <c r="D39" t="n">
-        <v>991</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="40">
@@ -4848,10 +5024,10 @@
         <v>48</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9303534303534303</v>
+        <v>0.9363295880149812</v>
       </c>
       <c r="D40" t="n">
-        <v>962</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="41">
@@ -4864,10 +5040,10 @@
         <v>50</v>
       </c>
       <c r="C41" t="n">
-        <v>0.935672514619883</v>
+        <v>0.9417989417989417</v>
       </c>
       <c r="D41" t="n">
-        <v>855</v>
+        <v>945</v>
       </c>
     </row>
     <row r="42">
@@ -5489,7 +5665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5932,26 +6108,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>3.290739216204042</v>
+        <v>4.112989772033381</v>
       </c>
       <c r="D18" t="n">
-        <v>7592</v>
+        <v>9248</v>
       </c>
       <c r="E18" t="n">
-        <v>3.000367647058824</v>
+        <v>4.228982843137255</v>
       </c>
       <c r="F18" t="n">
         <v>96</v>
       </c>
       <c r="G18" t="n">
-        <v>0.290371569145218</v>
+        <v>-0.1159930711038744</v>
       </c>
     </row>
     <row r="19">
@@ -5961,22 +6137,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>3.33243209735256</v>
+        <v>3.290739216204042</v>
       </c>
       <c r="D19" t="n">
-        <v>6176</v>
+        <v>7592</v>
       </c>
       <c r="E19" t="n">
-        <v>3.263541666666667</v>
+        <v>3.000367647058824</v>
       </c>
       <c r="F19" t="n">
         <v>96</v>
       </c>
       <c r="G19" t="n">
-        <v>0.06889043068589285</v>
+        <v>0.290371569145218</v>
       </c>
     </row>
     <row r="20">
@@ -5986,22 +6162,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>3.536591102906034</v>
+        <v>3.33243209735256</v>
       </c>
       <c r="D20" t="n">
-        <v>6296</v>
+        <v>6176</v>
       </c>
       <c r="E20" t="n">
-        <v>3.466299019607843</v>
+        <v>3.263541666666667</v>
       </c>
       <c r="F20" t="n">
         <v>96</v>
       </c>
       <c r="G20" t="n">
-        <v>0.07029208329819125</v>
+        <v>0.06889043068589285</v>
       </c>
     </row>
     <row r="21">
@@ -6011,22 +6187,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>3.663854489164087</v>
+        <v>3.536591102906034</v>
       </c>
       <c r="D21" t="n">
-        <v>5176</v>
+        <v>6296</v>
       </c>
       <c r="E21" t="n">
-        <v>3.814889705882353</v>
+        <v>3.466299019607843</v>
       </c>
       <c r="F21" t="n">
         <v>96</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1510352167182663</v>
+        <v>0.07029208329819125</v>
       </c>
     </row>
     <row r="22">
@@ -6036,22 +6212,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>3.743944564470195</v>
+        <v>3.663854489164087</v>
       </c>
       <c r="D22" t="n">
-        <v>4800</v>
+        <v>5176</v>
       </c>
       <c r="E22" t="n">
-        <v>4.007598039215686</v>
+        <v>3.814889705882353</v>
       </c>
       <c r="F22" t="n">
         <v>96</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2636534747454911</v>
+        <v>-0.1510352167182663</v>
       </c>
     </row>
     <row r="23">
@@ -6061,22 +6237,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>3.776677555295115</v>
+        <v>3.743944564470195</v>
       </c>
       <c r="D23" t="n">
-        <v>4728</v>
+        <v>4800</v>
       </c>
       <c r="E23" t="n">
-        <v>4.014460784313726</v>
+        <v>4.007598039215686</v>
       </c>
       <c r="F23" t="n">
         <v>96</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.237783229018611</v>
+        <v>-0.2636534747454911</v>
       </c>
     </row>
     <row r="24">
@@ -6086,22 +6262,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>3.889255298078827</v>
+        <v>3.776677555295115</v>
       </c>
       <c r="D24" t="n">
-        <v>4168</v>
+        <v>4728</v>
       </c>
       <c r="E24" t="n">
-        <v>4.15392156862745</v>
+        <v>4.014460784313726</v>
       </c>
       <c r="F24" t="n">
         <v>96</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2646662705486231</v>
+        <v>-0.237783229018611</v>
       </c>
     </row>
     <row r="25">
@@ -6111,22 +6287,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>4.005326146015042</v>
+        <v>3.889255298078827</v>
       </c>
       <c r="D25" t="n">
-        <v>4136</v>
+        <v>4168</v>
       </c>
       <c r="E25" t="n">
-        <v>4.129044117647059</v>
+        <v>4.15392156862745</v>
       </c>
       <c r="F25" t="n">
         <v>96</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1237179716320167</v>
+        <v>-0.2646662705486231</v>
       </c>
     </row>
     <row r="26">
@@ -6136,22 +6312,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>3.999240719910011</v>
+        <v>4.005326146015042</v>
       </c>
       <c r="D26" t="n">
-        <v>3568</v>
+        <v>4136</v>
       </c>
       <c r="E26" t="n">
-        <v>4.220649509803922</v>
+        <v>4.129044117647059</v>
       </c>
       <c r="F26" t="n">
         <v>96</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.2214087898939106</v>
+        <v>-0.1237179716320167</v>
       </c>
     </row>
     <row r="27">
@@ -6161,47 +6337,47 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27" t="n">
-        <v>4.077670148096037</v>
+        <v>3.999240719910011</v>
       </c>
       <c r="D27" t="n">
-        <v>3280</v>
+        <v>3568</v>
       </c>
       <c r="E27" t="n">
-        <v>4.238419117647059</v>
+        <v>4.220649509803922</v>
       </c>
       <c r="F27" t="n">
         <v>96</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.1607489695510216</v>
+        <v>-0.2214087898939106</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C28" t="n">
-        <v>3.291063332476854</v>
+        <v>4.077670148096037</v>
       </c>
       <c r="D28" t="n">
-        <v>7120</v>
+        <v>3280</v>
       </c>
       <c r="E28" t="n">
-        <v>3.003247549019608</v>
+        <v>4.238419117647059</v>
       </c>
       <c r="F28" t="n">
         <v>96</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2878157834572463</v>
+        <v>-0.1607489695510216</v>
       </c>
     </row>
     <row r="29">
@@ -6211,22 +6387,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>3.473938140701307</v>
+        <v>3.291063332476854</v>
       </c>
       <c r="D29" t="n">
-        <v>6696</v>
+        <v>7120</v>
       </c>
       <c r="E29" t="n">
-        <v>3.180759803921569</v>
+        <v>3.003247549019608</v>
       </c>
       <c r="F29" t="n">
         <v>96</v>
       </c>
       <c r="G29" t="n">
-        <v>0.293178336779738</v>
+        <v>0.2878157834572463</v>
       </c>
     </row>
     <row r="30">
@@ -6236,22 +6412,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>3.559655103991918</v>
+        <v>3.473938140701307</v>
       </c>
       <c r="D30" t="n">
-        <v>6528</v>
+        <v>6696</v>
       </c>
       <c r="E30" t="n">
-        <v>3.308026960784314</v>
+        <v>3.180759803921569</v>
       </c>
       <c r="F30" t="n">
         <v>96</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2516281432076046</v>
+        <v>0.293178336779738</v>
       </c>
     </row>
     <row r="31">
@@ -6261,22 +6437,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>3.789291932327125</v>
+        <v>3.559655103991918</v>
       </c>
       <c r="D31" t="n">
-        <v>4904</v>
+        <v>6528</v>
       </c>
       <c r="E31" t="n">
-        <v>3.674203431372549</v>
+        <v>3.308026960784314</v>
       </c>
       <c r="F31" t="n">
         <v>96</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1150885009545761</v>
+        <v>0.2516281432076046</v>
       </c>
     </row>
     <row r="32">
@@ -6286,22 +6462,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>3.866575385749644</v>
+        <v>3.789291932327125</v>
       </c>
       <c r="D32" t="n">
-        <v>3744</v>
+        <v>4904</v>
       </c>
       <c r="E32" t="n">
-        <v>3.887990196078432</v>
+        <v>3.674203431372549</v>
       </c>
       <c r="F32" t="n">
         <v>96</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.02141481032878723</v>
+        <v>0.1150885009545761</v>
       </c>
     </row>
     <row r="33">
@@ -6311,22 +6487,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>3.927499916586033</v>
+        <v>3.866575385749644</v>
       </c>
       <c r="D33" t="n">
-        <v>5304</v>
+        <v>3744</v>
       </c>
       <c r="E33" t="n">
-        <v>4.016544117647059</v>
+        <v>3.887990196078432</v>
       </c>
       <c r="F33" t="n">
         <v>96</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.08904420106102551</v>
+        <v>-0.02141481032878723</v>
       </c>
     </row>
     <row r="34">
@@ -6336,22 +6512,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>3.996886296418009</v>
+        <v>3.927499916586033</v>
       </c>
       <c r="D34" t="n">
-        <v>6456</v>
+        <v>5304</v>
       </c>
       <c r="E34" t="n">
-        <v>3.897120098039216</v>
+        <v>4.016544117647059</v>
       </c>
       <c r="F34" t="n">
         <v>96</v>
       </c>
       <c r="G34" t="n">
-        <v>0.09976619837879319</v>
+        <v>-0.08904420106102551</v>
       </c>
     </row>
     <row r="35">
@@ -6361,22 +6537,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>4.173726067180183</v>
+        <v>3.996886296418009</v>
       </c>
       <c r="D35" t="n">
-        <v>6136</v>
+        <v>6456</v>
       </c>
       <c r="E35" t="n">
-        <v>4.085416666666666</v>
+        <v>3.897120098039216</v>
       </c>
       <c r="F35" t="n">
         <v>96</v>
       </c>
       <c r="G35" t="n">
-        <v>0.08830940051351632</v>
+        <v>0.09976619837879319</v>
       </c>
     </row>
     <row r="36">
@@ -6386,22 +6562,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C36" t="n">
-        <v>4.104804034498446</v>
+        <v>4.173726067180183</v>
       </c>
       <c r="D36" t="n">
-        <v>6088</v>
+        <v>6136</v>
       </c>
       <c r="E36" t="n">
-        <v>4.143872549019608</v>
+        <v>4.085416666666666</v>
       </c>
       <c r="F36" t="n">
         <v>96</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.03906851452116111</v>
+        <v>0.08830940051351632</v>
       </c>
     </row>
     <row r="37">
@@ -6411,21 +6587,46 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C37" t="n">
-        <v>4.320434945333217</v>
+        <v>4.104804034498446</v>
       </c>
       <c r="D37" t="n">
-        <v>7408</v>
+        <v>6088</v>
       </c>
       <c r="E37" t="n">
-        <v>4.19718137254902</v>
+        <v>4.143872549019608</v>
       </c>
       <c r="F37" t="n">
         <v>96</v>
       </c>
       <c r="G37" t="n">
+        <v>-0.03906851452116111</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>9</v>
+      </c>
+      <c r="C38" t="n">
+        <v>4.320434945333217</v>
+      </c>
+      <c r="D38" t="n">
+        <v>7408</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4.19718137254902</v>
+      </c>
+      <c r="F38" t="n">
+        <v>96</v>
+      </c>
+      <c r="G38" t="n">
         <v>0.123253572784197</v>
       </c>
     </row>

--- a/Exp3_PTO_GRPO/eda/results/arms/training/tables/gpt-4o-mini/training.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/training/tables/gpt-4o-mini/training.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1125,34 +1125,34 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>7574</v>
+        <v>17216</v>
       </c>
       <c r="E20" t="n">
-        <v>3.290739216204042</v>
+        <v>4.256488492237043</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8046651305316942</v>
+        <v>0.7864309606645561</v>
       </c>
       <c r="G20" t="n">
-        <v>2.352941176470588</v>
+        <v>2.847058823529411</v>
       </c>
       <c r="H20" t="n">
-        <v>3.311764705882353</v>
+        <v>4.535294117647059</v>
       </c>
       <c r="I20" t="n">
-        <v>4.435294117647059</v>
+        <v>4.911764705882353</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1161,37 +1161,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D21" t="n">
-        <v>6168</v>
+        <v>18128</v>
       </c>
       <c r="E21" t="n">
-        <v>3.33243209735256</v>
+        <v>4.452882443798349</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7666601470607851</v>
+        <v>0.5907494698627799</v>
       </c>
       <c r="G21" t="n">
-        <v>2.302352941176471</v>
+        <v>3.641176470588235</v>
       </c>
       <c r="H21" t="n">
-        <v>3.435294117647059</v>
+        <v>4.68235294117647</v>
       </c>
       <c r="I21" t="n">
-        <v>4.405882352941177</v>
+        <v>4.911764705882353</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.005516328331862313</v>
       </c>
     </row>
     <row r="22">
@@ -1206,25 +1206,25 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>6277</v>
+        <v>7574</v>
       </c>
       <c r="E22" t="n">
-        <v>3.536591102906034</v>
+        <v>3.290739216204042</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6748374152512981</v>
+        <v>0.8046651305316942</v>
       </c>
       <c r="G22" t="n">
-        <v>2.647058823529412</v>
+        <v>2.352941176470588</v>
       </c>
       <c r="H22" t="n">
-        <v>3.470588235294118</v>
+        <v>3.311764705882353</v>
       </c>
       <c r="I22" t="n">
-        <v>4.476470588235294</v>
+        <v>4.435294117647059</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1242,22 +1242,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>5168</v>
+        <v>6168</v>
       </c>
       <c r="E23" t="n">
-        <v>3.663854489164087</v>
+        <v>3.33243209735256</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5430193468825506</v>
+        <v>0.7666601470607851</v>
       </c>
       <c r="G23" t="n">
-        <v>2.91764705882353</v>
+        <v>2.302352941176471</v>
       </c>
       <c r="H23" t="n">
-        <v>3.670588235294118</v>
+        <v>3.435294117647059</v>
       </c>
       <c r="I23" t="n">
         <v>4.405882352941177</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>4792</v>
+        <v>6277</v>
       </c>
       <c r="E24" t="n">
-        <v>3.743944564470195</v>
+        <v>3.536591102906034</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5762331485203405</v>
+        <v>0.6748374152512981</v>
       </c>
       <c r="G24" t="n">
-        <v>2.976470588235294</v>
+        <v>2.647058823529412</v>
       </c>
       <c r="H24" t="n">
-        <v>3.7</v>
+        <v>3.470588235294118</v>
       </c>
       <c r="I24" t="n">
-        <v>4.564705882352941</v>
+        <v>4.476470588235294</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1314,25 +1314,25 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>4718</v>
+        <v>5168</v>
       </c>
       <c r="E25" t="n">
-        <v>3.776677555295115</v>
+        <v>3.663854489164087</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5295341015127092</v>
+        <v>0.5430193468825506</v>
       </c>
       <c r="G25" t="n">
-        <v>3.076470588235294</v>
+        <v>2.91764705882353</v>
       </c>
       <c r="H25" t="n">
-        <v>3.735294117647059</v>
+        <v>3.670588235294118</v>
       </c>
       <c r="I25" t="n">
-        <v>4.552941176470588</v>
+        <v>4.405882352941177</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1350,25 +1350,25 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>4158</v>
+        <v>4792</v>
       </c>
       <c r="E26" t="n">
-        <v>3.889255298078827</v>
+        <v>3.743944564470195</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5741195003775807</v>
+        <v>0.5762331485203405</v>
       </c>
       <c r="G26" t="n">
-        <v>3.111764705882353</v>
+        <v>2.976470588235294</v>
       </c>
       <c r="H26" t="n">
-        <v>3.858823529411764</v>
+        <v>3.7</v>
       </c>
       <c r="I26" t="n">
-        <v>4.623529411764705</v>
+        <v>4.564705882352941</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1386,25 +1386,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>4114</v>
+        <v>4718</v>
       </c>
       <c r="E27" t="n">
-        <v>4.005326146015042</v>
+        <v>3.776677555295115</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5416210462718096</v>
+        <v>0.5295341015127092</v>
       </c>
       <c r="G27" t="n">
-        <v>3.370588235294118</v>
+        <v>3.076470588235294</v>
       </c>
       <c r="H27" t="n">
-        <v>3.858823529411764</v>
+        <v>3.735294117647059</v>
       </c>
       <c r="I27" t="n">
-        <v>4.823529411764707</v>
+        <v>4.552941176470588</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1422,25 +1422,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>3556</v>
+        <v>4158</v>
       </c>
       <c r="E28" t="n">
-        <v>3.999240719910011</v>
+        <v>3.889255298078827</v>
       </c>
       <c r="F28" t="n">
-        <v>0.513138129373051</v>
+        <v>0.5741195003775807</v>
       </c>
       <c r="G28" t="n">
-        <v>3.391176470588235</v>
+        <v>3.111764705882353</v>
       </c>
       <c r="H28" t="n">
-        <v>3.947058823529412</v>
+        <v>3.858823529411764</v>
       </c>
       <c r="I28" t="n">
-        <v>4.852941176470589</v>
+        <v>4.623529411764705</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1458,25 +1458,25 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>3261</v>
+        <v>4114</v>
       </c>
       <c r="E29" t="n">
-        <v>4.077670148096037</v>
+        <v>4.005326146015042</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5552196216842494</v>
+        <v>0.5416210462718096</v>
       </c>
       <c r="G29" t="n">
-        <v>3.329411764705882</v>
+        <v>3.370588235294118</v>
       </c>
       <c r="H29" t="n">
-        <v>4.117647058823529</v>
+        <v>3.858823529411764</v>
       </c>
       <c r="I29" t="n">
-        <v>4.852941176470589</v>
+        <v>4.823529411764707</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1485,7 +1485,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1494,25 +1494,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>7097</v>
+        <v>3556</v>
       </c>
       <c r="E30" t="n">
-        <v>3.291063332476854</v>
+        <v>3.999240719910011</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9647864799567627</v>
+        <v>0.513138129373051</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>3.391176470588235</v>
       </c>
       <c r="H30" t="n">
-        <v>3.435294117647059</v>
+        <v>3.947058823529412</v>
       </c>
       <c r="I30" t="n">
-        <v>4.535294117647059</v>
+        <v>4.852941176470589</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1530,25 +1530,25 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D31" t="n">
-        <v>6685</v>
+        <v>3261</v>
       </c>
       <c r="E31" t="n">
-        <v>3.473938140701307</v>
+        <v>4.077670148096037</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8816031388249556</v>
+        <v>0.5552196216842494</v>
       </c>
       <c r="G31" t="n">
-        <v>2.310588235294118</v>
+        <v>3.329411764705882</v>
       </c>
       <c r="H31" t="n">
-        <v>3.505882352941176</v>
+        <v>4.117647058823529</v>
       </c>
       <c r="I31" t="n">
-        <v>4.564705882352941</v>
+        <v>4.852941176470589</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1566,25 +1566,25 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>6522</v>
+        <v>7097</v>
       </c>
       <c r="E32" t="n">
-        <v>3.559655103991918</v>
+        <v>3.291063332476854</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8483398044383608</v>
+        <v>0.9647864799567627</v>
       </c>
       <c r="G32" t="n">
-        <v>2.382352941176471</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>3.623529411764706</v>
+        <v>3.435294117647059</v>
       </c>
       <c r="I32" t="n">
-        <v>4.594117647058823</v>
+        <v>4.535294117647059</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1602,25 +1602,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>4899</v>
+        <v>6685</v>
       </c>
       <c r="E33" t="n">
-        <v>3.789291932327125</v>
+        <v>3.473938140701307</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7231635892705964</v>
+        <v>0.8816031388249556</v>
       </c>
       <c r="G33" t="n">
-        <v>2.758823529411765</v>
+        <v>2.310588235294118</v>
       </c>
       <c r="H33" t="n">
-        <v>3.841176470588235</v>
+        <v>3.505882352941176</v>
       </c>
       <c r="I33" t="n">
-        <v>4.652941176470588</v>
+        <v>4.564705882352941</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1638,25 +1638,25 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>3351</v>
+        <v>6522</v>
       </c>
       <c r="E34" t="n">
-        <v>3.866575385749644</v>
+        <v>3.559655103991918</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7382916147127863</v>
+        <v>0.8483398044383608</v>
       </c>
       <c r="G34" t="n">
-        <v>2.817647058823529</v>
+        <v>2.382352941176471</v>
       </c>
       <c r="H34" t="n">
-        <v>3.982352941176471</v>
+        <v>3.623529411764706</v>
       </c>
       <c r="I34" t="n">
-        <v>4.794117647058823</v>
+        <v>4.594117647058823</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1674,25 +1674,25 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>5289</v>
+        <v>4899</v>
       </c>
       <c r="E35" t="n">
-        <v>3.927499916586033</v>
+        <v>3.789291932327125</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7053329596308401</v>
+        <v>0.7231635892705964</v>
       </c>
       <c r="G35" t="n">
-        <v>2.817647058823529</v>
+        <v>2.758823529411765</v>
       </c>
       <c r="H35" t="n">
-        <v>4.076470588235294</v>
+        <v>3.841176470588235</v>
       </c>
       <c r="I35" t="n">
-        <v>4.794117647058823</v>
+        <v>4.652941176470588</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1710,25 +1710,25 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>6444</v>
+        <v>3351</v>
       </c>
       <c r="E36" t="n">
-        <v>3.996886296418009</v>
+        <v>3.866575385749644</v>
       </c>
       <c r="F36" t="n">
-        <v>0.699194486280059</v>
+        <v>0.7382916147127863</v>
       </c>
       <c r="G36" t="n">
-        <v>2.847058823529411</v>
+        <v>2.817647058823529</v>
       </c>
       <c r="H36" t="n">
-        <v>4.158823529411764</v>
+        <v>3.982352941176471</v>
       </c>
       <c r="I36" t="n">
-        <v>4.882352941176471</v>
+        <v>4.794117647058823</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1746,25 +1746,25 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>6117</v>
+        <v>5289</v>
       </c>
       <c r="E37" t="n">
-        <v>4.173726067180183</v>
+        <v>3.927499916586033</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7248460576901864</v>
+        <v>0.7053329596308401</v>
       </c>
       <c r="G37" t="n">
         <v>2.817647058823529</v>
       </c>
       <c r="H37" t="n">
-        <v>4.376470588235295</v>
+        <v>4.076470588235294</v>
       </c>
       <c r="I37" t="n">
-        <v>4.911764705882353</v>
+        <v>4.794117647058823</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -1782,25 +1782,25 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D38" t="n">
-        <v>6077</v>
+        <v>6444</v>
       </c>
       <c r="E38" t="n">
-        <v>4.104804034498446</v>
+        <v>3.996886296418009</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6493581191361258</v>
+        <v>0.699194486280059</v>
       </c>
       <c r="G38" t="n">
-        <v>2.947058823529412</v>
+        <v>2.847058823529411</v>
       </c>
       <c r="H38" t="n">
-        <v>4.276470588235294</v>
+        <v>4.158823529411764</v>
       </c>
       <c r="I38" t="n">
-        <v>4.852941176470589</v>
+        <v>4.882352941176471</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -1818,27 +1818,99 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D39" t="n">
-        <v>7387</v>
+        <v>6117</v>
       </c>
       <c r="E39" t="n">
-        <v>4.320434945333217</v>
+        <v>4.173726067180183</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6017010582352287</v>
+        <v>0.7248460576901864</v>
       </c>
       <c r="G39" t="n">
-        <v>3.441176470588236</v>
+        <v>2.817647058823529</v>
       </c>
       <c r="H39" t="n">
-        <v>4.464705882352941</v>
+        <v>4.376470588235295</v>
       </c>
       <c r="I39" t="n">
         <v>4.911764705882353</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>9</v>
+      </c>
+      <c r="D40" t="n">
+        <v>6077</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4.104804034498446</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.6493581191361258</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.947058823529412</v>
+      </c>
+      <c r="H40" t="n">
+        <v>4.276470588235294</v>
+      </c>
+      <c r="I40" t="n">
+        <v>4.852941176470589</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>10</v>
+      </c>
+      <c r="D41" t="n">
+        <v>7387</v>
+      </c>
+      <c r="E41" t="n">
+        <v>4.320434945333217</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.6017010582352287</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3.441176470588236</v>
+      </c>
+      <c r="H41" t="n">
+        <v>4.464705882352941</v>
+      </c>
+      <c r="I41" t="n">
+        <v>4.911764705882353</v>
+      </c>
+      <c r="J41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1853,7 +1925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2338,55 +2410,49 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.09290360784749298</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2735077171015929</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.3217316082443207</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.2764705882352937</v>
-      </c>
-      <c r="I20" t="n">
-        <v>782</v>
+        <v>0.277319985659524</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.1814345991561181</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.07644579038152549</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2502057299603779</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.2988387588044927</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.2588235294117647</v>
-      </c>
-      <c r="I21" t="n">
-        <v>618</v>
+        <v>0.2247720523107382</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1634189548272808</v>
       </c>
     </row>
     <row r="22">
@@ -2401,19 +2467,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.24403916585694</v>
+        <v>0.2735077171015929</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2945635673624288</v>
+        <v>0.3217316082443207</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2588235294117647</v>
+        <v>0.2764705882352937</v>
       </c>
       <c r="I22" t="n">
-        <v>620</v>
+        <v>782</v>
       </c>
     </row>
     <row r="23">
@@ -2428,19 +2494,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2317847077007</v>
+        <v>0.2502057299603779</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2689969271290605</v>
+        <v>0.2988387588044927</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2352941176470589</v>
+        <v>0.2588235294117647</v>
       </c>
       <c r="I23" t="n">
-        <v>536</v>
+        <v>618</v>
       </c>
     </row>
     <row r="24">
@@ -2455,19 +2521,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2366862745098039</v>
+        <v>0.24403916585694</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2812324929971988</v>
+        <v>0.2945635673624288</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2470588235294118</v>
+        <v>0.2588235294117647</v>
       </c>
       <c r="I24" t="n">
-        <v>483</v>
+        <v>620</v>
       </c>
     </row>
     <row r="25">
@@ -2482,19 +2548,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2253110381208321</v>
+        <v>0.2317847077007</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2672693498452013</v>
+        <v>0.2689969271290605</v>
       </c>
       <c r="H25" t="n">
         <v>0.2352941176470589</v>
       </c>
       <c r="I25" t="n">
-        <v>475</v>
+        <v>536</v>
       </c>
     </row>
     <row r="26">
@@ -2509,19 +2575,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2201648413684092</v>
+        <v>0.2366862745098039</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2718382352941177</v>
+        <v>0.2812324929971988</v>
       </c>
       <c r="H26" t="n">
         <v>0.2470588235294118</v>
       </c>
       <c r="I26" t="n">
-        <v>400</v>
+        <v>483</v>
       </c>
     </row>
     <row r="27">
@@ -2536,19 +2602,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>0.195312322220958</v>
+        <v>0.2253110381208321</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2490765171503958</v>
+        <v>0.2672693498452013</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2294117647058824</v>
+        <v>0.2352941176470589</v>
       </c>
       <c r="I27" t="n">
-        <v>379</v>
+        <v>475</v>
       </c>
     </row>
     <row r="28">
@@ -2563,19 +2629,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2253363228699552</v>
+        <v>0.2201648413684092</v>
       </c>
       <c r="G28" t="n">
-        <v>0.265716147955027</v>
+        <v>0.2718382352941177</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2470588235294109</v>
+        <v>0.2470588235294118</v>
       </c>
       <c r="I28" t="n">
-        <v>361</v>
+        <v>400</v>
       </c>
     </row>
     <row r="29">
@@ -2590,25 +2656,25 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1957532281205165</v>
+        <v>0.195312322220958</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2667364454678668</v>
+        <v>0.2490765171503958</v>
       </c>
       <c r="H29" t="n">
         <v>0.2294117647058824</v>
       </c>
       <c r="I29" t="n">
-        <v>281</v>
+        <v>379</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2617,25 +2683,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4241705221414408</v>
+        <v>0.2253363228699552</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4512302036199095</v>
+        <v>0.265716147955027</v>
       </c>
       <c r="H30" t="n">
-        <v>0.391176470588235</v>
+        <v>0.2470588235294109</v>
       </c>
       <c r="I30" t="n">
-        <v>832</v>
+        <v>361</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2644,19 +2710,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E31" t="n">
-        <v>0.431745027760208</v>
+        <v>0.1957532281205165</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4614169060940571</v>
+        <v>0.2667364454678668</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4058823529411766</v>
+        <v>0.2294117647058824</v>
       </c>
       <c r="I31" t="n">
-        <v>778</v>
+        <v>281</v>
       </c>
     </row>
     <row r="32">
@@ -2671,19 +2737,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4447303921568627</v>
+        <v>0.4241705221414408</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4704503676470588</v>
+        <v>0.4512302036199095</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3970588235294117</v>
+        <v>0.391176470588235</v>
       </c>
       <c r="I32" t="n">
-        <v>768</v>
+        <v>832</v>
       </c>
     </row>
     <row r="33">
@@ -2698,19 +2764,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>0.396497457057864</v>
+        <v>0.431745027760208</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4260474349597744</v>
+        <v>0.4614169060940571</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3588235294117643</v>
+        <v>0.4058823529411766</v>
       </c>
       <c r="I33" t="n">
-        <v>563</v>
+        <v>778</v>
       </c>
     </row>
     <row r="34">
@@ -2725,19 +2791,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3809829059829061</v>
+        <v>0.4447303921568627</v>
       </c>
       <c r="G34" t="n">
-        <v>0.408632897603486</v>
+        <v>0.4704503676470588</v>
       </c>
       <c r="H34" t="n">
-        <v>0.3529411764705881</v>
+        <v>0.3970588235294117</v>
       </c>
       <c r="I34" t="n">
-        <v>432</v>
+        <v>768</v>
       </c>
     </row>
     <row r="35">
@@ -2752,19 +2818,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3324017389761335</v>
+        <v>0.396497457057864</v>
       </c>
       <c r="G35" t="n">
-        <v>0.3789560894780448</v>
+        <v>0.4260474349597744</v>
       </c>
       <c r="H35" t="n">
-        <v>0.3235294117647058</v>
+        <v>0.3588235294117643</v>
       </c>
       <c r="I35" t="n">
-        <v>568</v>
+        <v>563</v>
       </c>
     </row>
     <row r="36">
@@ -2779,19 +2845,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3317515853925214</v>
+        <v>0.3809829059829061</v>
       </c>
       <c r="G36" t="n">
-        <v>0.381601639204303</v>
+        <v>0.408632897603486</v>
       </c>
       <c r="H36" t="n">
-        <v>0.3352941176470585</v>
+        <v>0.3529411764705881</v>
       </c>
       <c r="I36" t="n">
-        <v>689</v>
+        <v>432</v>
       </c>
     </row>
     <row r="37">
@@ -2806,19 +2872,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2731497814249559</v>
+        <v>0.3324017389761335</v>
       </c>
       <c r="G37" t="n">
-        <v>0.3538677771993754</v>
+        <v>0.3789560894780448</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2588235294117656</v>
+        <v>0.3235294117647058</v>
       </c>
       <c r="I37" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
     </row>
     <row r="38">
@@ -2833,19 +2899,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3020483883435108</v>
+        <v>0.3317515853925214</v>
       </c>
       <c r="G38" t="n">
-        <v>0.3677736657576938</v>
+        <v>0.381601639204303</v>
       </c>
       <c r="H38" t="n">
-        <v>0.276470588235294</v>
+        <v>0.3352941176470585</v>
       </c>
       <c r="I38" t="n">
-        <v>604</v>
+        <v>689</v>
       </c>
     </row>
     <row r="39">
@@ -2860,18 +2926,72 @@
         </is>
       </c>
       <c r="C39" t="n">
+        <v>8</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.2731497814249559</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.3538677771993754</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.2588235294117656</v>
+      </c>
+      <c r="I39" t="n">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>9</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.3020483883435108</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.3677736657576938</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.276470588235294</v>
+      </c>
+      <c r="I40" t="n">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
         <v>10</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E41" t="n">
         <v>0.2335662558760005</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G41" t="n">
         <v>0.3282486414338833</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H41" t="n">
         <v>0.2352941176470589</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I41" t="n">
         <v>617</v>
       </c>
     </row>
@@ -2886,7 +3006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3438,57 +3558,57 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>7592</v>
+        <v>17216</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>3.290739216204042</v>
+        <v>4.256488492237043</v>
       </c>
       <c r="H20" t="n">
-        <v>286.2219441517387</v>
+        <v>983.246689126394</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C21" t="n">
-        <v>6176</v>
+        <v>18128</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G21" t="n">
-        <v>3.33243209735256</v>
+        <v>4.452882443798349</v>
       </c>
       <c r="H21" t="n">
-        <v>324.7984132124352</v>
+        <v>1011.604037952339</v>
       </c>
     </row>
     <row r="22">
@@ -3498,25 +3618,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>6296</v>
+        <v>7592</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>3.536591102906034</v>
+        <v>3.290739216204042</v>
       </c>
       <c r="H22" t="n">
-        <v>345.3122617534943</v>
+        <v>286.2219441517387</v>
       </c>
     </row>
     <row r="23">
@@ -3526,25 +3646,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>5176</v>
+        <v>6176</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>3.663854489164087</v>
+        <v>3.33243209735256</v>
       </c>
       <c r="H23" t="n">
-        <v>398.2600463678516</v>
+        <v>324.7984132124352</v>
       </c>
     </row>
     <row r="24">
@@ -3554,25 +3674,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>4800</v>
+        <v>6296</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.17</v>
+        <v>0.3</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>3.743944564470195</v>
+        <v>3.536591102906034</v>
       </c>
       <c r="H24" t="n">
-        <v>534.891875</v>
+        <v>345.3122617534943</v>
       </c>
     </row>
     <row r="25">
@@ -3582,25 +3702,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>4728</v>
+        <v>5176</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>3.776677555295115</v>
+        <v>3.663854489164087</v>
       </c>
       <c r="H25" t="n">
-        <v>609.8616751269036</v>
+        <v>398.2600463678516</v>
       </c>
     </row>
     <row r="26">
@@ -3610,25 +3730,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>4168</v>
+        <v>4800</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>3.889255298078827</v>
+        <v>3.743944564470195</v>
       </c>
       <c r="H26" t="n">
-        <v>740.5856525911709</v>
+        <v>534.891875</v>
       </c>
     </row>
     <row r="27">
@@ -3638,25 +3758,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>4136</v>
+        <v>4728</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.53</v>
+        <v>0.21</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>4.005326146015042</v>
+        <v>3.776677555295115</v>
       </c>
       <c r="H27" t="n">
-        <v>697.2487911025145</v>
+        <v>609.8616751269036</v>
       </c>
     </row>
     <row r="28">
@@ -3666,25 +3786,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C28" t="n">
-        <v>3568</v>
+        <v>4168</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.34</v>
+        <v>0.24</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>3.999240719910011</v>
+        <v>3.889255298078827</v>
       </c>
       <c r="H28" t="n">
-        <v>808.7051569506726</v>
+        <v>740.5856525911709</v>
       </c>
     </row>
     <row r="29">
@@ -3694,81 +3814,81 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C29" t="n">
-        <v>3280</v>
+        <v>4136</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>4.077670148096037</v>
+        <v>4.005326146015042</v>
       </c>
       <c r="H29" t="n">
-        <v>829.6390243902439</v>
+        <v>697.2487911025145</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C30" t="n">
-        <v>7120</v>
+        <v>3568</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>3.291063332476854</v>
+        <v>3.999240719910011</v>
       </c>
       <c r="H30" t="n">
-        <v>305.6846910112359</v>
+        <v>808.7051569506726</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>6696</v>
+        <v>3280</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.16</v>
+        <v>0.58</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>3.473938140701307</v>
+        <v>4.077670148096037</v>
       </c>
       <c r="H31" t="n">
-        <v>363.8626045400239</v>
+        <v>829.6390243902439</v>
       </c>
     </row>
     <row r="32">
@@ -3778,25 +3898,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>6528</v>
+        <v>7120</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.09</v>
+        <v>0.32</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>3.559655103991918</v>
+        <v>3.291063332476854</v>
       </c>
       <c r="H32" t="n">
-        <v>445.0816482843137</v>
+        <v>305.6846910112359</v>
       </c>
     </row>
     <row r="33">
@@ -3806,25 +3926,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>4904</v>
+        <v>6696</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>3.789291932327125</v>
+        <v>3.473938140701307</v>
       </c>
       <c r="H33" t="n">
-        <v>561.2230831973899</v>
+        <v>363.8626045400239</v>
       </c>
     </row>
     <row r="34">
@@ -3834,25 +3954,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>3744</v>
+        <v>6528</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>3.866575385749644</v>
+        <v>3.559655103991918</v>
       </c>
       <c r="H34" t="n">
-        <v>632.4281517094017</v>
+        <v>445.0816482843137</v>
       </c>
     </row>
     <row r="35">
@@ -3862,25 +3982,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>5304</v>
+        <v>4904</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0.28</v>
+        <v>0.1</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>3.927499916586033</v>
+        <v>3.789291932327125</v>
       </c>
       <c r="H35" t="n">
-        <v>752.7567873303168</v>
+        <v>561.2230831973899</v>
       </c>
     </row>
     <row r="36">
@@ -3890,25 +4010,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>6456</v>
+        <v>3744</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>3.996886296418009</v>
+        <v>3.866575385749644</v>
       </c>
       <c r="H36" t="n">
-        <v>836.0020136307311</v>
+        <v>632.4281517094017</v>
       </c>
     </row>
     <row r="37">
@@ -3918,25 +4038,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>6136</v>
+        <v>5304</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>4.173726067180183</v>
+        <v>3.927499916586033</v>
       </c>
       <c r="H37" t="n">
-        <v>936.5017926988266</v>
+        <v>752.7567873303168</v>
       </c>
     </row>
     <row r="38">
@@ -3946,25 +4066,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>6088</v>
+        <v>6456</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>4.104804034498446</v>
+        <v>3.996886296418009</v>
       </c>
       <c r="H38" t="n">
-        <v>960.3909329829172</v>
+        <v>836.0020136307311</v>
       </c>
     </row>
     <row r="39">
@@ -3974,24 +4094,80 @@
         </is>
       </c>
       <c r="B39" t="n">
+        <v>8</v>
+      </c>
+      <c r="C39" t="n">
+        <v>6136</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>4.173726067180183</v>
+      </c>
+      <c r="H39" t="n">
+        <v>936.5017926988266</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>9</v>
+      </c>
+      <c r="C40" t="n">
+        <v>6088</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>4.104804034498446</v>
+      </c>
+      <c r="H40" t="n">
+        <v>960.3909329829172</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
         <v>10</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C41" t="n">
         <v>7408</v>
       </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
         <v>0.28</v>
       </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
         <v>4.320434945333217</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H41" t="n">
         <v>1003.434260259179</v>
       </c>
     </row>
@@ -4044,7 +4220,7 @@
         <v>0.8599</v>
       </c>
       <c r="C2" t="n">
-        <v>0.876</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="D2" t="n">
         <v>0.8647</v>
@@ -4061,7 +4237,7 @@
         <v>0.872</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8944</v>
+        <v>0.9015</v>
       </c>
       <c r="D3" t="n">
         <v>0.8633999999999999</v>
@@ -4078,7 +4254,7 @@
         <v>0.8781</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.9072</v>
       </c>
       <c r="D4" t="n">
         <v>0.8577</v>
@@ -4095,7 +4271,7 @@
         <v>0.8758</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9026</v>
+        <v>0.9081</v>
       </c>
       <c r="D5" t="n">
         <v>0.8413</v>
@@ -4112,7 +4288,7 @@
         <v>0.8738</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9021</v>
+        <v>0.9087</v>
       </c>
       <c r="D6" t="n">
         <v>0.8247</v>
@@ -4129,7 +4305,7 @@
         <v>0.8768</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.9137</v>
       </c>
       <c r="D7" t="n">
         <v>0.8084</v>
@@ -4146,7 +4322,7 @@
         <v>0.8754</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9035</v>
+        <v>0.9161</v>
       </c>
       <c r="D8" t="n">
         <v>0.7887999999999999</v>
@@ -4163,7 +4339,7 @@
         <v>0.8739</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9086</v>
+        <v>0.9214</v>
       </c>
       <c r="D9" t="n">
         <v>0.7868000000000001</v>
@@ -4180,7 +4356,7 @@
         <v>0.8672</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9046999999999999</v>
+        <v>0.9207</v>
       </c>
       <c r="D10" t="n">
         <v>0.7837</v>
@@ -4197,7 +4373,7 @@
         <v>0.8738</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9066</v>
+        <v>0.9237</v>
       </c>
       <c r="D11" t="n">
         <v>0.7637</v>
@@ -4214,7 +4390,7 @@
         <v>0.8663</v>
       </c>
       <c r="C12" t="n">
-        <v>0.908</v>
+        <v>0.9286</v>
       </c>
       <c r="D12" t="n">
         <v>0.7633</v>
@@ -4231,7 +4407,7 @@
         <v>0.8737</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9084</v>
+        <v>0.9311</v>
       </c>
       <c r="D13" t="n">
         <v>0.7597</v>
@@ -4248,7 +4424,7 @@
         <v>0.8759</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9111</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="D14" t="n">
         <v>0.7668</v>
@@ -4265,7 +4441,7 @@
         <v>0.8725000000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9169</v>
+        <v>0.9342</v>
       </c>
       <c r="D15" t="n">
         <v>0.7654</v>
@@ -4282,7 +4458,7 @@
         <v>0.8822</v>
       </c>
       <c r="C16" t="n">
-        <v>0.929</v>
+        <v>0.9399</v>
       </c>
       <c r="D16" t="n">
         <v>0.7581</v>
@@ -4299,7 +4475,7 @@
         <v>0.8842</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9298999999999999</v>
+        <v>0.9421</v>
       </c>
       <c r="D17" t="n">
         <v>0.7376</v>
@@ -4316,7 +4492,7 @@
         <v>0.8744</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9284</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="D18" t="n">
         <v>0.7478</v>
@@ -4333,7 +4509,7 @@
         <v>0.8815</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9281</v>
+        <v>0.9306</v>
       </c>
       <c r="D19" t="n">
         <v>0.7574</v>
@@ -4350,7 +4526,7 @@
         <v>0.8925999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9363</v>
+        <v>0.9401</v>
       </c>
       <c r="D20" t="n">
         <v>0.7561</v>
@@ -4367,7 +4543,7 @@
         <v>0.8968</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9418</v>
+        <v>0.9357</v>
       </c>
     </row>
   </sheetData>
@@ -4736,10 +4912,10 @@
         <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>0.875998003992016</v>
+        <v>0.8855815811816411</v>
       </c>
       <c r="D22" t="n">
-        <v>28056</v>
+        <v>40046</v>
       </c>
     </row>
     <row r="23">
@@ -4752,10 +4928,10 @@
         <v>14</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8943778732383751</v>
+        <v>0.9014757846601538</v>
       </c>
       <c r="D23" t="n">
-        <v>26538</v>
+        <v>38488</v>
       </c>
     </row>
     <row r="24">
@@ -4768,10 +4944,10 @@
         <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9006824636513925</v>
+        <v>0.907182862751891</v>
       </c>
       <c r="D24" t="n">
-        <v>23591</v>
+        <v>34638</v>
       </c>
     </row>
     <row r="25">
@@ -4784,10 +4960,10 @@
         <v>18</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9026370217166494</v>
+        <v>0.9081082959719181</v>
       </c>
       <c r="D25" t="n">
-        <v>19340</v>
+        <v>28773</v>
       </c>
     </row>
     <row r="26">
@@ -4800,10 +4976,10 @@
         <v>20</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9020856344616984</v>
+        <v>0.9087437789600137</v>
       </c>
       <c r="D26" t="n">
-        <v>15391</v>
+        <v>23308</v>
       </c>
     </row>
     <row r="27">
@@ -4816,10 +4992,10 @@
         <v>22</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9027194896760115</v>
+        <v>0.9137191854233655</v>
       </c>
       <c r="D27" t="n">
-        <v>11914</v>
+        <v>18660</v>
       </c>
     </row>
     <row r="28">
@@ -4832,10 +5008,10 @@
         <v>24</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9034546934977318</v>
+        <v>0.9161139858610888</v>
       </c>
       <c r="D28" t="n">
-        <v>8597</v>
+        <v>13721</v>
       </c>
     </row>
     <row r="29">
@@ -4848,10 +5024,10 @@
         <v>26</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9085868424996254</v>
+        <v>0.9213781728214057</v>
       </c>
       <c r="D29" t="n">
-        <v>6673</v>
+        <v>10913</v>
       </c>
     </row>
     <row r="30">
@@ -4864,10 +5040,10 @@
         <v>28</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9047185279650209</v>
+        <v>0.9206783369803063</v>
       </c>
       <c r="D30" t="n">
-        <v>5489</v>
+        <v>9140</v>
       </c>
     </row>
     <row r="31">
@@ -4880,10 +5056,10 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9065662508825606</v>
+        <v>0.9237253005388973</v>
       </c>
       <c r="D31" t="n">
-        <v>4249</v>
+        <v>7237</v>
       </c>
     </row>
     <row r="32">
@@ -4896,10 +5072,10 @@
         <v>32</v>
       </c>
       <c r="C32" t="n">
-        <v>0.908005164622337</v>
+        <v>0.928597854236034</v>
       </c>
       <c r="D32" t="n">
-        <v>3098</v>
+        <v>5406</v>
       </c>
     </row>
     <row r="33">
@@ -4912,10 +5088,10 @@
         <v>34</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9083747927031509</v>
+        <v>0.9311121116614138</v>
       </c>
       <c r="D33" t="n">
-        <v>2412</v>
+        <v>4442</v>
       </c>
     </row>
     <row r="34">
@@ -4928,10 +5104,10 @@
         <v>36</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9111006585136406</v>
+        <v>0.9298804780876494</v>
       </c>
       <c r="D34" t="n">
-        <v>2126</v>
+        <v>3765</v>
       </c>
     </row>
     <row r="35">
@@ -4944,10 +5120,10 @@
         <v>38</v>
       </c>
       <c r="C35" t="n">
-        <v>0.9168646080760094</v>
+        <v>0.9341935483870968</v>
       </c>
       <c r="D35" t="n">
-        <v>1684</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="36">
@@ -4960,10 +5136,10 @@
         <v>40</v>
       </c>
       <c r="C36" t="n">
-        <v>0.92904953145917</v>
+        <v>0.9398948159278738</v>
       </c>
       <c r="D36" t="n">
-        <v>1494</v>
+        <v>2662</v>
       </c>
     </row>
     <row r="37">
@@ -4976,10 +5152,10 @@
         <v>42</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9298507462686567</v>
+        <v>0.9420529801324503</v>
       </c>
       <c r="D37" t="n">
-        <v>1340</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="38">
@@ -4992,10 +5168,10 @@
         <v>44</v>
       </c>
       <c r="C38" t="n">
-        <v>0.9283970707892596</v>
+        <v>0.9389521640091116</v>
       </c>
       <c r="D38" t="n">
-        <v>1229</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="39">
@@ -5008,10 +5184,10 @@
         <v>46</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9280701754385965</v>
+        <v>0.9305887984681666</v>
       </c>
       <c r="D39" t="n">
-        <v>1140</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="40">
@@ -5024,10 +5200,10 @@
         <v>48</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9363295880149812</v>
+        <v>0.9401041666666666</v>
       </c>
       <c r="D40" t="n">
-        <v>1068</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="41">
@@ -5040,10 +5216,10 @@
         <v>50</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9417989417989417</v>
+        <v>0.9356894553881807</v>
       </c>
       <c r="D41" t="n">
-        <v>945</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="42">
@@ -5665,7 +5841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6133,76 +6309,76 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>3.290739216204042</v>
+        <v>4.093557233704293</v>
       </c>
       <c r="D19" t="n">
-        <v>7592</v>
+        <v>14800</v>
       </c>
       <c r="E19" t="n">
-        <v>3.000367647058824</v>
+        <v>4.270098039215687</v>
       </c>
       <c r="F19" t="n">
         <v>96</v>
       </c>
       <c r="G19" t="n">
-        <v>0.290371569145218</v>
+        <v>-0.1765408055113937</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>3.33243209735256</v>
+        <v>4.256488492237043</v>
       </c>
       <c r="D20" t="n">
-        <v>6176</v>
+        <v>17216</v>
       </c>
       <c r="E20" t="n">
-        <v>3.263541666666667</v>
+        <v>4.254411764705883</v>
       </c>
       <c r="F20" t="n">
         <v>96</v>
       </c>
       <c r="G20" t="n">
-        <v>0.06889043068589285</v>
+        <v>0.002076727531160394</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>3.536591102906034</v>
+        <v>4.452882443798349</v>
       </c>
       <c r="D21" t="n">
-        <v>6296</v>
+        <v>18128</v>
       </c>
       <c r="E21" t="n">
-        <v>3.466299019607843</v>
+        <v>4.454473039215686</v>
       </c>
       <c r="F21" t="n">
         <v>96</v>
       </c>
       <c r="G21" t="n">
-        <v>0.07029208329819125</v>
+        <v>-0.001590595417336971</v>
       </c>
     </row>
     <row r="22">
@@ -6212,22 +6388,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>3.663854489164087</v>
+        <v>3.290739216204042</v>
       </c>
       <c r="D22" t="n">
-        <v>5176</v>
+        <v>7592</v>
       </c>
       <c r="E22" t="n">
-        <v>3.814889705882353</v>
+        <v>3.000367647058824</v>
       </c>
       <c r="F22" t="n">
         <v>96</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1510352167182663</v>
+        <v>0.290371569145218</v>
       </c>
     </row>
     <row r="23">
@@ -6237,22 +6413,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>3.743944564470195</v>
+        <v>3.33243209735256</v>
       </c>
       <c r="D23" t="n">
-        <v>4800</v>
+        <v>6176</v>
       </c>
       <c r="E23" t="n">
-        <v>4.007598039215686</v>
+        <v>3.263541666666667</v>
       </c>
       <c r="F23" t="n">
         <v>96</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2636534747454911</v>
+        <v>0.06889043068589285</v>
       </c>
     </row>
     <row r="24">
@@ -6262,22 +6438,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>3.776677555295115</v>
+        <v>3.536591102906034</v>
       </c>
       <c r="D24" t="n">
-        <v>4728</v>
+        <v>6296</v>
       </c>
       <c r="E24" t="n">
-        <v>4.014460784313726</v>
+        <v>3.466299019607843</v>
       </c>
       <c r="F24" t="n">
         <v>96</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.237783229018611</v>
+        <v>0.07029208329819125</v>
       </c>
     </row>
     <row r="25">
@@ -6287,22 +6463,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>3.889255298078827</v>
+        <v>3.663854489164087</v>
       </c>
       <c r="D25" t="n">
-        <v>4168</v>
+        <v>5176</v>
       </c>
       <c r="E25" t="n">
-        <v>4.15392156862745</v>
+        <v>3.814889705882353</v>
       </c>
       <c r="F25" t="n">
         <v>96</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2646662705486231</v>
+        <v>-0.1510352167182663</v>
       </c>
     </row>
     <row r="26">
@@ -6312,22 +6488,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>4.005326146015042</v>
+        <v>3.743944564470195</v>
       </c>
       <c r="D26" t="n">
-        <v>4136</v>
+        <v>4800</v>
       </c>
       <c r="E26" t="n">
-        <v>4.129044117647059</v>
+        <v>4.007598039215686</v>
       </c>
       <c r="F26" t="n">
         <v>96</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.1237179716320167</v>
+        <v>-0.2636534747454911</v>
       </c>
     </row>
     <row r="27">
@@ -6337,22 +6513,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>3.999240719910011</v>
+        <v>3.776677555295115</v>
       </c>
       <c r="D27" t="n">
-        <v>3568</v>
+        <v>4728</v>
       </c>
       <c r="E27" t="n">
-        <v>4.220649509803922</v>
+        <v>4.014460784313726</v>
       </c>
       <c r="F27" t="n">
         <v>96</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.2214087898939106</v>
+        <v>-0.237783229018611</v>
       </c>
     </row>
     <row r="28">
@@ -6362,97 +6538,97 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>4.077670148096037</v>
+        <v>3.889255298078827</v>
       </c>
       <c r="D28" t="n">
-        <v>3280</v>
+        <v>4168</v>
       </c>
       <c r="E28" t="n">
-        <v>4.238419117647059</v>
+        <v>4.15392156862745</v>
       </c>
       <c r="F28" t="n">
         <v>96</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.1607489695510216</v>
+        <v>-0.2646662705486231</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C29" t="n">
-        <v>3.291063332476854</v>
+        <v>4.005326146015042</v>
       </c>
       <c r="D29" t="n">
-        <v>7120</v>
+        <v>4136</v>
       </c>
       <c r="E29" t="n">
-        <v>3.003247549019608</v>
+        <v>4.129044117647059</v>
       </c>
       <c r="F29" t="n">
         <v>96</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2878157834572463</v>
+        <v>-0.1237179716320167</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C30" t="n">
-        <v>3.473938140701307</v>
+        <v>3.999240719910011</v>
       </c>
       <c r="D30" t="n">
-        <v>6696</v>
+        <v>3568</v>
       </c>
       <c r="E30" t="n">
-        <v>3.180759803921569</v>
+        <v>4.220649509803922</v>
       </c>
       <c r="F30" t="n">
         <v>96</v>
       </c>
       <c r="G30" t="n">
-        <v>0.293178336779738</v>
+        <v>-0.2214087898939106</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C31" t="n">
-        <v>3.559655103991918</v>
+        <v>4.077670148096037</v>
       </c>
       <c r="D31" t="n">
-        <v>6528</v>
+        <v>3280</v>
       </c>
       <c r="E31" t="n">
-        <v>3.308026960784314</v>
+        <v>4.238419117647059</v>
       </c>
       <c r="F31" t="n">
         <v>96</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2516281432076046</v>
+        <v>-0.1607489695510216</v>
       </c>
     </row>
     <row r="32">
@@ -6462,22 +6638,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>3.789291932327125</v>
+        <v>3.291063332476854</v>
       </c>
       <c r="D32" t="n">
-        <v>4904</v>
+        <v>7120</v>
       </c>
       <c r="E32" t="n">
-        <v>3.674203431372549</v>
+        <v>3.003247549019608</v>
       </c>
       <c r="F32" t="n">
         <v>96</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1150885009545761</v>
+        <v>0.2878157834572463</v>
       </c>
     </row>
     <row r="33">
@@ -6487,22 +6663,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>3.866575385749644</v>
+        <v>3.473938140701307</v>
       </c>
       <c r="D33" t="n">
-        <v>3744</v>
+        <v>6696</v>
       </c>
       <c r="E33" t="n">
-        <v>3.887990196078432</v>
+        <v>3.180759803921569</v>
       </c>
       <c r="F33" t="n">
         <v>96</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.02141481032878723</v>
+        <v>0.293178336779738</v>
       </c>
     </row>
     <row r="34">
@@ -6512,22 +6688,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>3.927499916586033</v>
+        <v>3.559655103991918</v>
       </c>
       <c r="D34" t="n">
-        <v>5304</v>
+        <v>6528</v>
       </c>
       <c r="E34" t="n">
-        <v>4.016544117647059</v>
+        <v>3.308026960784314</v>
       </c>
       <c r="F34" t="n">
         <v>96</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.08904420106102551</v>
+        <v>0.2516281432076046</v>
       </c>
     </row>
     <row r="35">
@@ -6537,22 +6713,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>3.996886296418009</v>
+        <v>3.789291932327125</v>
       </c>
       <c r="D35" t="n">
-        <v>6456</v>
+        <v>4904</v>
       </c>
       <c r="E35" t="n">
-        <v>3.897120098039216</v>
+        <v>3.674203431372549</v>
       </c>
       <c r="F35" t="n">
         <v>96</v>
       </c>
       <c r="G35" t="n">
-        <v>0.09976619837879319</v>
+        <v>0.1150885009545761</v>
       </c>
     </row>
     <row r="36">
@@ -6562,22 +6738,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>4.173726067180183</v>
+        <v>3.866575385749644</v>
       </c>
       <c r="D36" t="n">
-        <v>6136</v>
+        <v>3744</v>
       </c>
       <c r="E36" t="n">
-        <v>4.085416666666666</v>
+        <v>3.887990196078432</v>
       </c>
       <c r="F36" t="n">
         <v>96</v>
       </c>
       <c r="G36" t="n">
-        <v>0.08830940051351632</v>
+        <v>-0.02141481032878723</v>
       </c>
     </row>
     <row r="37">
@@ -6587,22 +6763,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>4.104804034498446</v>
+        <v>3.927499916586033</v>
       </c>
       <c r="D37" t="n">
-        <v>6088</v>
+        <v>5304</v>
       </c>
       <c r="E37" t="n">
-        <v>4.143872549019608</v>
+        <v>4.016544117647059</v>
       </c>
       <c r="F37" t="n">
         <v>96</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.03906851452116111</v>
+        <v>-0.08904420106102551</v>
       </c>
     </row>
     <row r="38">
@@ -6612,21 +6788,96 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C38" t="n">
-        <v>4.320434945333217</v>
+        <v>3.996886296418009</v>
       </c>
       <c r="D38" t="n">
-        <v>7408</v>
+        <v>6456</v>
       </c>
       <c r="E38" t="n">
-        <v>4.19718137254902</v>
+        <v>3.897120098039216</v>
       </c>
       <c r="F38" t="n">
         <v>96</v>
       </c>
       <c r="G38" t="n">
+        <v>0.09976619837879319</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>7</v>
+      </c>
+      <c r="C39" t="n">
+        <v>4.173726067180183</v>
+      </c>
+      <c r="D39" t="n">
+        <v>6136</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4.085416666666666</v>
+      </c>
+      <c r="F39" t="n">
+        <v>96</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.08830940051351632</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>8</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4.104804034498446</v>
+      </c>
+      <c r="D40" t="n">
+        <v>6088</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4.143872549019608</v>
+      </c>
+      <c r="F40" t="n">
+        <v>96</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-0.03906851452116111</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>9</v>
+      </c>
+      <c r="C41" t="n">
+        <v>4.320434945333217</v>
+      </c>
+      <c r="D41" t="n">
+        <v>7408</v>
+      </c>
+      <c r="E41" t="n">
+        <v>4.19718137254902</v>
+      </c>
+      <c r="F41" t="n">
+        <v>96</v>
+      </c>
+      <c r="G41" t="n">
         <v>0.123253572784197</v>
       </c>
     </row>
